--- a/data/output/sim_gridrnd/REL1/group_500_60/results/REL1_G6_results_summary.xlsx
+++ b/data/output/sim_gridrnd/REL1/group_500_60/results/REL1_G6_results_summary.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CM23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,24 +436,24 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>mu</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sigma</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>jnd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>pse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>jnd</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sigma</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mu</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_trials</t>
@@ -466,1106 +466,1260 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>lat_entropy_100</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_120</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_140</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_160</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_180</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_200</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_40</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_60</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_80</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pse_40</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>jnd_40</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>pse_60</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>jnd_60</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pse_80</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>jnd_80</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>pse_100</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>jnd_100</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pse_120</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>jnd_120</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>pse_140</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>jnd_140</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>pse_160</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>jnd_160</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>pse_180</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>jnd_180</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>pse_200</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>jnd_200</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_40</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_60</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_80</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_100</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_120</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_140</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_160</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_180</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_200</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_40</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_60</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_80</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_100</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_120</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_140</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_160</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_180</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_200</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_40</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_60</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_80</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_100</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_120</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_140</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_160</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_180</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_200</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_40</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_60</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_80</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_100</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_120</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_140</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_160</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_180</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_200</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_40</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_60</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_80</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_100</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_120</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_140</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_160</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_180</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_200</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_40</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_60</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_80</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_100</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_120</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_140</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_160</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_180</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_200</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>pse_est</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>jnd_est</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S02_G6_499_58_REL1</t>
+          <t>S01_G6_498_59_REL1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C2" t="n">
-        <v>58</v>
+        <v>87.47220163083766</v>
       </c>
       <c r="D2" t="n">
-        <v>85.9896219421794</v>
+        <v>59</v>
       </c>
       <c r="E2" t="n">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F2" t="n">
         <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>502.9744964983638</v>
-      </c>
-      <c r="J2" t="n">
-        <v>62.45793816229445</v>
-      </c>
-      <c r="K2" t="n">
-        <v>517.9283538285171</v>
-      </c>
-      <c r="L2" t="n">
-        <v>71.51601602778996</v>
-      </c>
-      <c r="M2" t="n">
-        <v>498.0935790307557</v>
-      </c>
-      <c r="N2" t="n">
-        <v>72.93422698917757</v>
-      </c>
-      <c r="O2" t="n">
-        <v>497.9317815771491</v>
-      </c>
-      <c r="P2" t="n">
-        <v>71.2758103012786</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>498.4600084016781</v>
-      </c>
       <c r="R2" t="n">
-        <v>67.76684915245305</v>
+        <v>458.3</v>
       </c>
       <c r="S2" t="n">
-        <v>492.6911622862242</v>
+        <v>76.13</v>
       </c>
       <c r="T2" t="n">
-        <v>66.99848251152949</v>
+        <v>492.66</v>
       </c>
       <c r="U2" t="n">
-        <v>496.5678550462916</v>
+        <v>82.91</v>
       </c>
       <c r="V2" t="n">
-        <v>69.2629581827769</v>
+        <v>493.38</v>
       </c>
       <c r="W2" t="n">
-        <v>494.8249841551292</v>
+        <v>82.06</v>
       </c>
       <c r="X2" t="n">
-        <v>70.75785289555813</v>
+        <v>488.54</v>
       </c>
       <c r="Y2" t="n">
-        <v>495.9744625123762</v>
+        <v>82.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>68.38124108377859</v>
+        <v>493.61</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>497.23</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>77.09</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>498.49</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>74.03</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>499.02</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>73.13</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>495.84</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>68.63</v>
       </c>
       <c r="AJ2" t="n">
-        <v>503.775</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>502.15</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>502.8</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>501.72</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>501.5666666666667</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>502.1571428571428</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>500.86875</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>500.5833333333333</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>501.02</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>104.0104532006279</v>
+        <v>500</v>
       </c>
       <c r="AT2" t="n">
-        <v>91.64566274516213</v>
+        <v>499.55</v>
       </c>
       <c r="AU2" t="n">
-        <v>90.27269797674157</v>
+        <v>498.55</v>
       </c>
       <c r="AV2" t="n">
-        <v>89.21816855327171</v>
+        <v>499.82</v>
       </c>
       <c r="AW2" t="n">
-        <v>85.60342023281287</v>
+        <v>499.8583333333333</v>
       </c>
       <c r="AX2" t="n">
-        <v>82.85014625632158</v>
+        <v>499.8928571428572</v>
       </c>
       <c r="AY2" t="n">
-        <v>81.22138895289528</v>
+        <v>500.6875</v>
       </c>
       <c r="AZ2" t="n">
-        <v>84.18847077308811</v>
+        <v>500.9555555555556</v>
       </c>
       <c r="BA2" t="n">
-        <v>82.26244343562863</v>
+        <v>500.69</v>
       </c>
       <c r="BB2" t="n">
-        <v>275</v>
+        <v>95.32470823453906</v>
       </c>
       <c r="BC2" t="n">
-        <v>275</v>
+        <v>89.24879551007957</v>
       </c>
       <c r="BD2" t="n">
-        <v>275</v>
+        <v>88.29565391342884</v>
       </c>
       <c r="BE2" t="n">
-        <v>275</v>
+        <v>84.36141060935385</v>
       </c>
       <c r="BF2" t="n">
-        <v>275</v>
+        <v>84.56854181011335</v>
       </c>
       <c r="BG2" t="n">
-        <v>275</v>
+        <v>83.18702649783211</v>
       </c>
       <c r="BH2" t="n">
-        <v>275</v>
+        <v>81.13423965102527</v>
       </c>
       <c r="BI2" t="n">
-        <v>275</v>
+        <v>78.65436501429828</v>
       </c>
       <c r="BJ2" t="n">
-        <v>275</v>
+        <v>75.1440210529088</v>
       </c>
       <c r="BK2" t="n">
-        <v>718</v>
+        <v>382</v>
       </c>
       <c r="BL2" t="n">
-        <v>718</v>
+        <v>382</v>
       </c>
       <c r="BM2" t="n">
-        <v>718</v>
+        <v>382</v>
       </c>
       <c r="BN2" t="n">
-        <v>718</v>
+        <v>382</v>
       </c>
       <c r="BO2" t="n">
-        <v>718</v>
+        <v>379</v>
       </c>
       <c r="BP2" t="n">
-        <v>718</v>
+        <v>377</v>
       </c>
       <c r="BQ2" t="n">
-        <v>718</v>
+        <v>377</v>
       </c>
       <c r="BR2" t="n">
-        <v>718</v>
+        <v>377</v>
       </c>
       <c r="BS2" t="n">
-        <v>718</v>
+        <v>377</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.875</v>
+        <v>669</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.875</v>
+        <v>669</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.8333333333333334</v>
+        <v>669</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.95</v>
+        <v>669</v>
       </c>
       <c r="BY2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="CK2" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="BZ2" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0.9666666666666667</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>0.9696969696969697</v>
+      <c r="CL2" t="n">
+        <v>495.84</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>68.63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S03_G6_500_58_REL1</t>
+          <t>S02_G6_499_58_REL1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C3" t="n">
+        <v>85.9896219421794</v>
+      </c>
+      <c r="D3" t="n">
         <v>58</v>
       </c>
-      <c r="D3" t="n">
-        <v>85.9896219421794</v>
-      </c>
       <c r="E3" t="n">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F3" t="n">
         <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>518.7286382258401</v>
-      </c>
-      <c r="J3" t="n">
-        <v>85.41747464773998</v>
-      </c>
-      <c r="K3" t="n">
-        <v>506.6513756835441</v>
-      </c>
-      <c r="L3" t="n">
-        <v>64.35107293936807</v>
-      </c>
-      <c r="M3" t="n">
-        <v>519.4064236655743</v>
-      </c>
-      <c r="N3" t="n">
-        <v>63.71335228224824</v>
-      </c>
-      <c r="O3" t="n">
-        <v>508.5202981873634</v>
-      </c>
-      <c r="P3" t="n">
-        <v>60.6231366480501</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>505.6957673615584</v>
-      </c>
       <c r="R3" t="n">
-        <v>64.43388729000534</v>
+        <v>502.97</v>
       </c>
       <c r="S3" t="n">
-        <v>505.5220582279476</v>
+        <v>62.46</v>
       </c>
       <c r="T3" t="n">
-        <v>67.01247826578297</v>
+        <v>517.9299999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>501.961321460046</v>
+        <v>71.52</v>
       </c>
       <c r="V3" t="n">
-        <v>66.35102577395907</v>
+        <v>498.09</v>
       </c>
       <c r="W3" t="n">
-        <v>502.2114489915477</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="X3" t="n">
-        <v>67.64741219975896</v>
+        <v>497.93</v>
       </c>
       <c r="Y3" t="n">
-        <v>502.2242556868571</v>
+        <v>71.28</v>
       </c>
       <c r="Z3" t="n">
-        <v>76.43687641354886</v>
+        <v>498.46</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>67.77</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>492.69</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>496.57</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>494.82</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>70.76000000000001</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>495.97</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>68.38</v>
       </c>
       <c r="AJ3" t="n">
-        <v>500.925</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>501.5833333333333</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>500.25</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>500.21</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>501.0583333333333</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>499.2</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>498.2875</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>498.8944444444444</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>498.935</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>84.83289087965822</v>
+        <v>503.775</v>
       </c>
       <c r="AT3" t="n">
-        <v>80.1565742087877</v>
+        <v>502.15</v>
       </c>
       <c r="AU3" t="n">
-        <v>74.73662087624781</v>
+        <v>502.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>70.24632303544436</v>
+        <v>501.72</v>
       </c>
       <c r="AW3" t="n">
-        <v>72.9137956577644</v>
+        <v>501.5666666666667</v>
       </c>
       <c r="AX3" t="n">
-        <v>74.13223705938309</v>
+        <v>502.1571428571428</v>
       </c>
       <c r="AY3" t="n">
-        <v>73.96412876354321</v>
+        <v>500.86875</v>
       </c>
       <c r="AZ3" t="n">
-        <v>72.61699351332014</v>
+        <v>500.5833333333333</v>
       </c>
       <c r="BA3" t="n">
-        <v>80.51640065849938</v>
+        <v>501.02</v>
       </c>
       <c r="BB3" t="n">
-        <v>387</v>
+        <v>104.0104532006279</v>
       </c>
       <c r="BC3" t="n">
-        <v>387</v>
+        <v>91.64566274516213</v>
       </c>
       <c r="BD3" t="n">
-        <v>387</v>
+        <v>90.27269797674157</v>
       </c>
       <c r="BE3" t="n">
-        <v>387</v>
+        <v>89.21816855327171</v>
       </c>
       <c r="BF3" t="n">
-        <v>387</v>
+        <v>85.60342023281287</v>
       </c>
       <c r="BG3" t="n">
-        <v>378</v>
+        <v>82.85014625632158</v>
       </c>
       <c r="BH3" t="n">
-        <v>375</v>
+        <v>81.22138895289528</v>
       </c>
       <c r="BI3" t="n">
-        <v>368</v>
+        <v>84.18847077308811</v>
       </c>
       <c r="BJ3" t="n">
-        <v>358</v>
+        <v>82.26244343562863</v>
       </c>
       <c r="BK3" t="n">
-        <v>669</v>
+        <v>275</v>
       </c>
       <c r="BL3" t="n">
-        <v>669</v>
+        <v>275</v>
       </c>
       <c r="BM3" t="n">
-        <v>669</v>
+        <v>275</v>
       </c>
       <c r="BN3" t="n">
-        <v>669</v>
+        <v>275</v>
       </c>
       <c r="BO3" t="n">
-        <v>669</v>
+        <v>275</v>
       </c>
       <c r="BP3" t="n">
-        <v>669</v>
+        <v>275</v>
       </c>
       <c r="BQ3" t="n">
-        <v>669</v>
+        <v>275</v>
       </c>
       <c r="BR3" t="n">
-        <v>669</v>
+        <v>275</v>
       </c>
       <c r="BS3" t="n">
-        <v>669</v>
+        <v>275</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.75</v>
+        <v>718</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.6842105263157895</v>
+        <v>718</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.7368421052631579</v>
+        <v>718</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.7368421052631579</v>
+        <v>718</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.7368421052631579</v>
+        <v>718</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.9230769230769231</v>
+        <v>718</v>
       </c>
       <c r="BZ3" t="n">
+        <v>718</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>718</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>718</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD3" t="n">
         <v>0.875</v>
       </c>
-      <c r="CA3" t="n">
-        <v>0.9333333333333333</v>
-      </c>
-      <c r="CB3" t="n">
+      <c r="CE3" t="n">
         <v>0.875</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>495.97</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>68.38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S01_G6_498_59_REL1</t>
+          <t>S03_G6_500_58_REL1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C4" t="n">
-        <v>59</v>
+        <v>85.9896219421794</v>
       </c>
       <c r="D4" t="n">
-        <v>87.47220163083766</v>
+        <v>58</v>
       </c>
       <c r="E4" t="n">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F4" t="n">
         <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>458.2966810179934</v>
-      </c>
-      <c r="J4" t="n">
-        <v>76.1252880037385</v>
-      </c>
-      <c r="K4" t="n">
-        <v>492.6551052362621</v>
-      </c>
-      <c r="L4" t="n">
-        <v>82.91309566355453</v>
-      </c>
-      <c r="M4" t="n">
-        <v>493.3752415347384</v>
-      </c>
-      <c r="N4" t="n">
-        <v>82.06272766408507</v>
-      </c>
-      <c r="O4" t="n">
-        <v>488.5431137750574</v>
-      </c>
-      <c r="P4" t="n">
-        <v>82.12479797816933</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>493.6126132850475</v>
-      </c>
       <c r="R4" t="n">
-        <v>82.75686959215753</v>
+        <v>518.73</v>
       </c>
       <c r="S4" t="n">
-        <v>497.2323610063812</v>
+        <v>85.42</v>
       </c>
       <c r="T4" t="n">
-        <v>77.08749257251711</v>
+        <v>506.65</v>
       </c>
       <c r="U4" t="n">
-        <v>498.4923180373939</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>74.02570521148834</v>
+        <v>519.41</v>
       </c>
       <c r="W4" t="n">
-        <v>499.0166382750059</v>
+        <v>63.71</v>
       </c>
       <c r="X4" t="n">
-        <v>73.12785658116024</v>
+        <v>508.52</v>
       </c>
       <c r="Y4" t="n">
-        <v>495.8424730982294</v>
+        <v>60.62</v>
       </c>
       <c r="Z4" t="n">
-        <v>68.62637272964889</v>
+        <v>505.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>505.52</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>501.96</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>502.21</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>502.22</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>76.44</v>
       </c>
       <c r="AJ4" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>499.55</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>498.55</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>499.82</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>499.8583333333333</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>499.8928571428572</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>500.6875</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>500.9555555555556</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>500.69</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>95.32470823453906</v>
+        <v>500.925</v>
       </c>
       <c r="AT4" t="n">
-        <v>89.24879551007957</v>
+        <v>501.5833333333333</v>
       </c>
       <c r="AU4" t="n">
-        <v>88.29565391342884</v>
+        <v>500.25</v>
       </c>
       <c r="AV4" t="n">
-        <v>84.36141060935385</v>
+        <v>500.21</v>
       </c>
       <c r="AW4" t="n">
-        <v>84.56854181011335</v>
+        <v>501.0583333333333</v>
       </c>
       <c r="AX4" t="n">
-        <v>83.18702649783211</v>
+        <v>499.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>81.13423965102527</v>
+        <v>498.2875</v>
       </c>
       <c r="AZ4" t="n">
-        <v>78.65436501429828</v>
+        <v>498.8944444444444</v>
       </c>
       <c r="BA4" t="n">
-        <v>75.1440210529088</v>
+        <v>498.935</v>
       </c>
       <c r="BB4" t="n">
-        <v>382</v>
+        <v>84.83289087965822</v>
       </c>
       <c r="BC4" t="n">
-        <v>382</v>
+        <v>80.1565742087877</v>
       </c>
       <c r="BD4" t="n">
-        <v>382</v>
+        <v>74.73662087624781</v>
       </c>
       <c r="BE4" t="n">
-        <v>382</v>
+        <v>70.24632303544436</v>
       </c>
       <c r="BF4" t="n">
-        <v>379</v>
+        <v>72.9137956577644</v>
       </c>
       <c r="BG4" t="n">
-        <v>377</v>
+        <v>74.13223705938309</v>
       </c>
       <c r="BH4" t="n">
-        <v>377</v>
+        <v>73.96412876354321</v>
       </c>
       <c r="BI4" t="n">
-        <v>377</v>
+        <v>72.61699351332014</v>
       </c>
       <c r="BJ4" t="n">
-        <v>377</v>
+        <v>80.51640065849938</v>
       </c>
       <c r="BK4" t="n">
-        <v>669</v>
+        <v>387</v>
       </c>
       <c r="BL4" t="n">
-        <v>669</v>
+        <v>387</v>
       </c>
       <c r="BM4" t="n">
-        <v>669</v>
+        <v>387</v>
       </c>
       <c r="BN4" t="n">
-        <v>669</v>
+        <v>387</v>
       </c>
       <c r="BO4" t="n">
-        <v>669</v>
+        <v>387</v>
       </c>
       <c r="BP4" t="n">
-        <v>669</v>
+        <v>378</v>
       </c>
       <c r="BQ4" t="n">
-        <v>669</v>
+        <v>375</v>
       </c>
       <c r="BR4" t="n">
-        <v>669</v>
+        <v>368</v>
       </c>
       <c r="BS4" t="n">
-        <v>669</v>
+        <v>358</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.6923076923076923</v>
+        <v>669</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.7692307692307693</v>
+        <v>669</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.8125</v>
+        <v>669</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.9411764705882353</v>
+        <v>669</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.8</v>
+        <v>669</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.7272727272727273</v>
+        <v>669</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.7272727272727273</v>
+        <v>669</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.9090909090909091</v>
+        <v>669</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.9166666666666666</v>
+        <v>669</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0.6842105263157895</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>502.22</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>76.44</v>
       </c>
     </row>
     <row r="5">
@@ -1578,10 +1732,10 @@
         <v>501</v>
       </c>
       <c r="C5" t="n">
+        <v>85.9896219421794</v>
+      </c>
+      <c r="D5" t="n">
         <v>58</v>
-      </c>
-      <c r="D5" t="n">
-        <v>85.9896219421794</v>
       </c>
       <c r="E5" t="n">
         <v>501</v>
@@ -1590,228 +1744,261 @@
         <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H5" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>472.2418400304459</v>
-      </c>
-      <c r="J5" t="n">
-        <v>86.8180692116874</v>
-      </c>
-      <c r="K5" t="n">
-        <v>475.000381718841</v>
-      </c>
-      <c r="L5" t="n">
-        <v>91.15205108923537</v>
-      </c>
-      <c r="M5" t="n">
-        <v>487.6617256303372</v>
-      </c>
-      <c r="N5" t="n">
-        <v>78.49866181054058</v>
-      </c>
-      <c r="O5" t="n">
-        <v>490.6205277269286</v>
-      </c>
-      <c r="P5" t="n">
-        <v>71.90118671540571</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>501.8094055845093</v>
-      </c>
       <c r="R5" t="n">
-        <v>73.46431609574682</v>
+        <v>472.24</v>
       </c>
       <c r="S5" t="n">
-        <v>501.7670958610312</v>
+        <v>86.81999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>72.99799490904478</v>
+        <v>475</v>
       </c>
       <c r="U5" t="n">
-        <v>499.596604894215</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>74.03632719027573</v>
+        <v>487.66</v>
       </c>
       <c r="W5" t="n">
-        <v>500.9912899994109</v>
+        <v>78.5</v>
       </c>
       <c r="X5" t="n">
-        <v>72.69072360064142</v>
+        <v>490.62</v>
       </c>
       <c r="Y5" t="n">
-        <v>500.4606374679794</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Z5" t="n">
-        <v>72.48307474265864</v>
+        <v>501.81</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>501.77</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>499.6</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>500.99</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>72.69</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>500.46</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>72.48</v>
       </c>
       <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
         <v>499.925</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AT5" t="n">
         <v>499.5666666666667</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AU5" t="n">
         <v>499.375</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AV5" t="n">
         <v>499.49</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AW5" t="n">
         <v>498.6916666666667</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AX5" t="n">
         <v>499.0928571428572</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="AY5" t="n">
         <v>499.625</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AZ5" t="n">
         <v>499.1222222222222</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="BA5" t="n">
         <v>498.855</v>
       </c>
-      <c r="AS5" t="n">
+      <c r="BB5" t="n">
         <v>127.8128294616781</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="BC5" t="n">
         <v>116.3705814294241</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="BD5" t="n">
         <v>110.3536785748441</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="BE5" t="n">
         <v>104.8146454461398</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="BF5" t="n">
         <v>98.02030366488137</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="BG5" t="n">
         <v>92.60707288851965</v>
       </c>
-      <c r="AY5" t="n">
+      <c r="BH5" t="n">
         <v>88.58504035671034</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BI5" t="n">
         <v>86.39191420211831</v>
       </c>
-      <c r="BA5" t="n">
+      <c r="BJ5" t="n">
         <v>85.67288938164745</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BK5" t="n">
         <v>309</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BL5" t="n">
         <v>309</v>
       </c>
-      <c r="BD5" t="n">
+      <c r="BM5" t="n">
         <v>309</v>
       </c>
-      <c r="BE5" t="n">
+      <c r="BN5" t="n">
         <v>309</v>
       </c>
-      <c r="BF5" t="n">
+      <c r="BO5" t="n">
         <v>309</v>
       </c>
-      <c r="BG5" t="n">
+      <c r="BP5" t="n">
         <v>309</v>
       </c>
-      <c r="BH5" t="n">
+      <c r="BQ5" t="n">
         <v>309</v>
       </c>
-      <c r="BI5" t="n">
+      <c r="BR5" t="n">
         <v>309</v>
       </c>
-      <c r="BJ5" t="n">
+      <c r="BS5" t="n">
         <v>309</v>
       </c>
-      <c r="BK5" t="n">
+      <c r="BT5" t="n">
         <v>676</v>
       </c>
-      <c r="BL5" t="n">
+      <c r="BU5" t="n">
         <v>676</v>
       </c>
-      <c r="BM5" t="n">
+      <c r="BV5" t="n">
         <v>676</v>
       </c>
-      <c r="BN5" t="n">
+      <c r="BW5" t="n">
         <v>676</v>
       </c>
-      <c r="BO5" t="n">
+      <c r="BX5" t="n">
         <v>676</v>
       </c>
-      <c r="BP5" t="n">
+      <c r="BY5" t="n">
         <v>676</v>
       </c>
-      <c r="BQ5" t="n">
+      <c r="BZ5" t="n">
         <v>676</v>
       </c>
-      <c r="BR5" t="n">
+      <c r="CA5" t="n">
         <v>676</v>
       </c>
-      <c r="BS5" t="n">
+      <c r="CB5" t="n">
         <v>676</v>
       </c>
-      <c r="BT5" t="n">
+      <c r="CC5" t="n">
         <v>0.5</v>
       </c>
-      <c r="BU5" t="n">
+      <c r="CD5" t="n">
         <v>0.75</v>
       </c>
-      <c r="BV5" t="n">
+      <c r="CE5" t="n">
         <v>0.8076923076923077</v>
       </c>
-      <c r="BW5" t="n">
+      <c r="CF5" t="n">
         <v>0.8</v>
       </c>
-      <c r="BX5" t="n">
+      <c r="CG5" t="n">
         <v>0.8</v>
       </c>
-      <c r="BY5" t="n">
+      <c r="CH5" t="n">
         <v>0.8</v>
       </c>
-      <c r="BZ5" t="n">
+      <c r="CI5" t="n">
         <v>0.7741935483870968</v>
       </c>
-      <c r="CA5" t="n">
+      <c r="CJ5" t="n">
         <v>0.8484848484848485</v>
       </c>
-      <c r="CB5" t="n">
+      <c r="CK5" t="n">
         <v>0.8157894736842105</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>500.46</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>72.48</v>
       </c>
     </row>
     <row r="6">
@@ -1824,10 +2011,10 @@
         <v>498</v>
       </c>
       <c r="C6" t="n">
+        <v>91.91994069681246</v>
+      </c>
+      <c r="D6" t="n">
         <v>62</v>
-      </c>
-      <c r="D6" t="n">
-        <v>91.91994069681246</v>
       </c>
       <c r="E6" t="n">
         <v>498</v>
@@ -1836,228 +2023,261 @@
         <v>200</v>
       </c>
       <c r="G6" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H6" t="inlineStr">
+        <v>76</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>458.2733533543208</v>
-      </c>
-      <c r="J6" t="n">
-        <v>60.53276011557552</v>
-      </c>
-      <c r="K6" t="n">
-        <v>487.0927104771116</v>
-      </c>
-      <c r="L6" t="n">
-        <v>58.03232477673718</v>
-      </c>
-      <c r="M6" t="n">
-        <v>487.4861920152204</v>
-      </c>
-      <c r="N6" t="n">
-        <v>58.03938983743333</v>
-      </c>
-      <c r="O6" t="n">
-        <v>482.5826826748136</v>
-      </c>
-      <c r="P6" t="n">
-        <v>59.56812972182141</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>482.9426422224277</v>
-      </c>
       <c r="R6" t="n">
-        <v>61.21493097887989</v>
+        <v>458.27</v>
       </c>
       <c r="S6" t="n">
-        <v>488.0056085059802</v>
+        <v>60.53</v>
       </c>
       <c r="T6" t="n">
-        <v>60.8735320914229</v>
+        <v>487.09</v>
       </c>
       <c r="U6" t="n">
-        <v>490.5528698855306</v>
+        <v>58.03</v>
       </c>
       <c r="V6" t="n">
-        <v>70.1543556512099</v>
+        <v>487.49</v>
       </c>
       <c r="W6" t="n">
-        <v>491.581212288961</v>
+        <v>58.04</v>
       </c>
       <c r="X6" t="n">
-        <v>74.37337950742479</v>
+        <v>482.58</v>
       </c>
       <c r="Y6" t="n">
-        <v>493.6846044542661</v>
+        <v>59.57</v>
       </c>
       <c r="Z6" t="n">
-        <v>74.19904241808278</v>
+        <v>482.94</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>61.21</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>488.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>60.87</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>490.55</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>491.58</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>74.37</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>493.68</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>74.2</v>
       </c>
       <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
         <v>504.75</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AT6" t="n">
         <v>502.1</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AU6" t="n">
         <v>501.625</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AV6" t="n">
         <v>501.67</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AW6" t="n">
         <v>501.0333333333334</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="AX6" t="n">
         <v>501.3214285714286</v>
       </c>
-      <c r="AP6" t="n">
+      <c r="AY6" t="n">
         <v>500.55</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AZ6" t="n">
         <v>501.0833333333333</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="BA6" t="n">
         <v>500.66</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="BB6" t="n">
         <v>100.0306827928311</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="BC6" t="n">
         <v>90.37877700728934</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="BD6" t="n">
         <v>82.67018431695917</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="BE6" t="n">
         <v>75.87068669782816</v>
       </c>
-      <c r="AW6" t="n">
+      <c r="BF6" t="n">
         <v>74.14748066447632</v>
       </c>
-      <c r="AX6" t="n">
+      <c r="BG6" t="n">
         <v>73.05313798453668</v>
       </c>
-      <c r="AY6" t="n">
+      <c r="BH6" t="n">
         <v>72.3223513168647</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BI6" t="n">
         <v>76.36577731185903</v>
       </c>
-      <c r="BA6" t="n">
+      <c r="BJ6" t="n">
         <v>79.11039375455036</v>
       </c>
-      <c r="BB6" t="n">
+      <c r="BK6" t="n">
         <v>388</v>
       </c>
-      <c r="BC6" t="n">
+      <c r="BL6" t="n">
         <v>388</v>
       </c>
-      <c r="BD6" t="n">
+      <c r="BM6" t="n">
         <v>388</v>
       </c>
-      <c r="BE6" t="n">
+      <c r="BN6" t="n">
         <v>388</v>
       </c>
-      <c r="BF6" t="n">
+      <c r="BO6" t="n">
         <v>388</v>
       </c>
-      <c r="BG6" t="n">
+      <c r="BP6" t="n">
         <v>388</v>
       </c>
-      <c r="BH6" t="n">
+      <c r="BQ6" t="n">
         <v>388</v>
       </c>
-      <c r="BI6" t="n">
+      <c r="BR6" t="n">
         <v>379</v>
       </c>
-      <c r="BJ6" t="n">
+      <c r="BS6" t="n">
         <v>379</v>
       </c>
-      <c r="BK6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>669</v>
-      </c>
       <c r="BT6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC6" t="n">
         <v>0.75</v>
       </c>
-      <c r="BU6" t="n">
+      <c r="CD6" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BV6" t="n">
+      <c r="CE6" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="BW6" t="n">
+      <c r="CF6" t="n">
         <v>1</v>
       </c>
-      <c r="BX6" t="n">
+      <c r="CG6" t="n">
         <v>1</v>
       </c>
-      <c r="BY6" t="n">
+      <c r="CH6" t="n">
         <v>0.875</v>
       </c>
-      <c r="BZ6" t="n">
+      <c r="CI6" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="CA6" t="n">
+      <c r="CJ6" t="n">
         <v>0.9375</v>
       </c>
-      <c r="CB6" t="n">
+      <c r="CK6" t="n">
         <v>0.7391304347826086</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>493.68</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>74.2</v>
       </c>
     </row>
     <row r="7">
@@ -2070,10 +2290,10 @@
         <v>499</v>
       </c>
       <c r="C7" t="n">
+        <v>85.9896219421794</v>
+      </c>
+      <c r="D7" t="n">
         <v>58</v>
-      </c>
-      <c r="D7" t="n">
-        <v>85.9896219421794</v>
       </c>
       <c r="E7" t="n">
         <v>499</v>
@@ -2082,720 +2302,819 @@
         <v>200</v>
       </c>
       <c r="G7" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>486.128104375665</v>
-      </c>
-      <c r="J7" t="n">
-        <v>60.29505348236696</v>
-      </c>
-      <c r="K7" t="n">
-        <v>497.2869564072996</v>
-      </c>
-      <c r="L7" t="n">
-        <v>88.36743683007946</v>
-      </c>
-      <c r="M7" t="n">
-        <v>487.83747633183</v>
-      </c>
-      <c r="N7" t="n">
-        <v>96.31882644702527</v>
-      </c>
-      <c r="O7" t="n">
-        <v>490.2117247435974</v>
-      </c>
-      <c r="P7" t="n">
-        <v>92.10607196914107</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>488.5203055711581</v>
-      </c>
       <c r="R7" t="n">
-        <v>85.75018336255887</v>
+        <v>486.13</v>
       </c>
       <c r="S7" t="n">
-        <v>483.5688200995781</v>
+        <v>60.3</v>
       </c>
       <c r="T7" t="n">
-        <v>81.13130295095218</v>
+        <v>497.29</v>
       </c>
       <c r="U7" t="n">
-        <v>484.7033377734707</v>
+        <v>88.37</v>
       </c>
       <c r="V7" t="n">
-        <v>76.37368369085922</v>
+        <v>487.84</v>
       </c>
       <c r="W7" t="n">
-        <v>485.4471792185737</v>
+        <v>96.31999999999999</v>
       </c>
       <c r="X7" t="n">
-        <v>75.43093040793759</v>
+        <v>490.21</v>
       </c>
       <c r="Y7" t="n">
-        <v>484.7311506767305</v>
+        <v>92.11</v>
       </c>
       <c r="Z7" t="n">
-        <v>73.15027948091786</v>
+        <v>488.52</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>85.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>483.57</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>81.13</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>484.7</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>76.37</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>485.45</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>484.73</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
         <v>499.075</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AT7" t="n">
         <v>498.6833333333333</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AU7" t="n">
         <v>499.075</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AV7" t="n">
         <v>499.2</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AW7" t="n">
         <v>499.1833333333333</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AX7" t="n">
         <v>497.8571428571428</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AY7" t="n">
         <v>498.29375</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AZ7" t="n">
         <v>498.5555555555555</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="BA7" t="n">
         <v>499.27</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="BB7" t="n">
         <v>104.0130730966065</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="BC7" t="n">
         <v>95.74558156327052</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="BD7" t="n">
         <v>96.31222339350288</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="BE7" t="n">
         <v>97.18631590918548</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="BF7" t="n">
         <v>94.59906477104072</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="BG7" t="n">
         <v>91.87970174002926</v>
       </c>
-      <c r="AY7" t="n">
+      <c r="BH7" t="n">
         <v>86.69851475623732</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BI7" t="n">
         <v>82.01383502679575</v>
       </c>
-      <c r="BA7" t="n">
+      <c r="BJ7" t="n">
         <v>79.69766056792382</v>
       </c>
-      <c r="BB7" t="n">
+      <c r="BK7" t="n">
         <v>351</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BL7" t="n">
         <v>351</v>
       </c>
-      <c r="BD7" t="n">
+      <c r="BM7" t="n">
         <v>351</v>
       </c>
-      <c r="BE7" t="n">
+      <c r="BN7" t="n">
         <v>351</v>
       </c>
-      <c r="BF7" t="n">
+      <c r="BO7" t="n">
         <v>351</v>
       </c>
-      <c r="BG7" t="n">
+      <c r="BP7" t="n">
         <v>351</v>
       </c>
-      <c r="BH7" t="n">
+      <c r="BQ7" t="n">
         <v>351</v>
       </c>
-      <c r="BI7" t="n">
+      <c r="BR7" t="n">
         <v>351</v>
       </c>
-      <c r="BJ7" t="n">
+      <c r="BS7" t="n">
         <v>351</v>
       </c>
-      <c r="BK7" t="n">
+      <c r="BT7" t="n">
         <v>684</v>
       </c>
-      <c r="BL7" t="n">
+      <c r="BU7" t="n">
         <v>684</v>
       </c>
-      <c r="BM7" t="n">
+      <c r="BV7" t="n">
         <v>684</v>
       </c>
-      <c r="BN7" t="n">
+      <c r="BW7" t="n">
         <v>684</v>
       </c>
-      <c r="BO7" t="n">
+      <c r="BX7" t="n">
         <v>684</v>
       </c>
-      <c r="BP7" t="n">
+      <c r="BY7" t="n">
         <v>684</v>
       </c>
-      <c r="BQ7" t="n">
+      <c r="BZ7" t="n">
         <v>684</v>
       </c>
-      <c r="BR7" t="n">
+      <c r="CA7" t="n">
         <v>684</v>
       </c>
-      <c r="BS7" t="n">
+      <c r="CB7" t="n">
         <v>684</v>
       </c>
-      <c r="BT7" t="n">
+      <c r="CC7" t="n">
         <v>1</v>
       </c>
-      <c r="BU7" t="n">
+      <c r="CD7" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="BV7" t="n">
+      <c r="CE7" t="n">
         <v>0.9</v>
       </c>
-      <c r="BW7" t="n">
+      <c r="CF7" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="BX7" t="n">
+      <c r="CG7" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="BY7" t="n">
+      <c r="CH7" t="n">
         <v>0.875</v>
       </c>
-      <c r="BZ7" t="n">
+      <c r="CI7" t="n">
         <v>0.9375</v>
       </c>
-      <c r="CA7" t="n">
+      <c r="CJ7" t="n">
         <v>0.9375</v>
       </c>
-      <c r="CB7" t="n">
+      <c r="CK7" t="n">
         <v>1</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>484.73</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>73.15000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S08_G6_501_60_REL1</t>
+          <t>S07_G6_499_58_REL1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C8" t="n">
-        <v>60</v>
+        <v>85.9896219421794</v>
       </c>
       <c r="D8" t="n">
-        <v>88.95478131949592</v>
+        <v>58</v>
       </c>
       <c r="E8" t="n">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="F8" t="n">
         <v>200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="H8" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>479.6150035369415</v>
-      </c>
-      <c r="J8" t="n">
-        <v>77.06295912574973</v>
-      </c>
-      <c r="K8" t="n">
-        <v>486.6443301033555</v>
-      </c>
-      <c r="L8" t="n">
-        <v>64.3699941394741</v>
-      </c>
-      <c r="M8" t="n">
-        <v>491.2727482128691</v>
-      </c>
-      <c r="N8" t="n">
-        <v>69.97706467088932</v>
-      </c>
-      <c r="O8" t="n">
-        <v>489.7120498731854</v>
-      </c>
-      <c r="P8" t="n">
-        <v>66.42513896559362</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>493.0668601786041</v>
-      </c>
       <c r="R8" t="n">
-        <v>65.14826609525109</v>
+        <v>503.7</v>
       </c>
       <c r="S8" t="n">
-        <v>495.1150492787311</v>
+        <v>43.67</v>
       </c>
       <c r="T8" t="n">
-        <v>62.33334753620908</v>
+        <v>497.32</v>
       </c>
       <c r="U8" t="n">
-        <v>495.6500871173467</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>61.1930303993867</v>
+        <v>497.66</v>
       </c>
       <c r="W8" t="n">
-        <v>492.62993137338</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>57.59963938770537</v>
+        <v>498.37</v>
       </c>
       <c r="Y8" t="n">
-        <v>490.5256399971348</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="Z8" t="n">
-        <v>58.02494902188568</v>
+        <v>492.91</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>489.47</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>66.86</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>487.72</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>490.79</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>61.58</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>491.56</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>63.78</v>
       </c>
       <c r="AJ8" t="n">
-        <v>499.775</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>499.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>499.875</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>499.26</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>500.8833333333333</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>499.55</v>
+        <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>499.51875</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>500.4611111111111</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>500.19</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>92.21943599372096</v>
+        <v>495.175</v>
       </c>
       <c r="AT8" t="n">
-        <v>86.11284586066252</v>
+        <v>496.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>80.67610783249276</v>
+        <v>497.275</v>
       </c>
       <c r="AV8" t="n">
-        <v>74.20062263889704</v>
+        <v>497.88</v>
       </c>
       <c r="AW8" t="n">
-        <v>72.60064087565313</v>
+        <v>497.7833333333334</v>
       </c>
       <c r="AX8" t="n">
-        <v>70.01758197563156</v>
+        <v>497.8714285714286</v>
       </c>
       <c r="AY8" t="n">
-        <v>68.94136746857797</v>
+        <v>498.4625</v>
       </c>
       <c r="AZ8" t="n">
-        <v>67.9131278332751</v>
+        <v>499.6388888888889</v>
       </c>
       <c r="BA8" t="n">
-        <v>67.14442568076669</v>
+        <v>499.65</v>
       </c>
       <c r="BB8" t="n">
-        <v>355</v>
+        <v>68.0028997543487</v>
       </c>
       <c r="BC8" t="n">
-        <v>355</v>
+        <v>66.22718475067471</v>
       </c>
       <c r="BD8" t="n">
-        <v>355</v>
+        <v>78.32065101236073</v>
       </c>
       <c r="BE8" t="n">
-        <v>355</v>
+        <v>83.19762977393046</v>
       </c>
       <c r="BF8" t="n">
-        <v>355</v>
+        <v>80.30319455386289</v>
       </c>
       <c r="BG8" t="n">
-        <v>355</v>
+        <v>78.10239093259409</v>
       </c>
       <c r="BH8" t="n">
-        <v>355</v>
+        <v>76.01191415659785</v>
       </c>
       <c r="BI8" t="n">
-        <v>355</v>
+        <v>73.83327794496711</v>
       </c>
       <c r="BJ8" t="n">
-        <v>355</v>
+        <v>73.95699764052081</v>
       </c>
       <c r="BK8" t="n">
-        <v>669</v>
+        <v>317</v>
       </c>
       <c r="BL8" t="n">
-        <v>669</v>
+        <v>317</v>
       </c>
       <c r="BM8" t="n">
-        <v>669</v>
+        <v>317</v>
       </c>
       <c r="BN8" t="n">
-        <v>669</v>
+        <v>317</v>
       </c>
       <c r="BO8" t="n">
-        <v>669</v>
+        <v>317</v>
       </c>
       <c r="BP8" t="n">
-        <v>669</v>
+        <v>317</v>
       </c>
       <c r="BQ8" t="n">
-        <v>669</v>
+        <v>317</v>
       </c>
       <c r="BR8" t="n">
-        <v>669</v>
+        <v>317</v>
       </c>
       <c r="BS8" t="n">
-        <v>669</v>
+        <v>317</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.7857142857142857</v>
+        <v>640</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.7222222222222222</v>
+        <v>640</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.7777777777777778</v>
+        <v>640</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.7777777777777778</v>
+        <v>640</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.8333333333333334</v>
+        <v>640</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.8888888888888888</v>
+        <v>640</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1</v>
+        <v>640</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.8076923076923077</v>
+        <v>640</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.7741935483870968</v>
+        <v>640</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0.7666666666666667</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>491.56</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>63.78</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S07_G6_499_58_REL1</t>
+          <t>S08_G6_501_60_REL1</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C9" t="n">
-        <v>58</v>
+        <v>88.95478131949592</v>
       </c>
       <c r="D9" t="n">
-        <v>85.9896219421794</v>
+        <v>60</v>
       </c>
       <c r="E9" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F9" t="n">
         <v>200</v>
       </c>
       <c r="G9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="H9" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>503.6995826223039</v>
-      </c>
-      <c r="J9" t="n">
-        <v>43.66522509023909</v>
-      </c>
-      <c r="K9" t="n">
-        <v>497.3218296079508</v>
-      </c>
-      <c r="L9" t="n">
-        <v>70.31707048159294</v>
-      </c>
-      <c r="M9" t="n">
-        <v>497.6573799412693</v>
-      </c>
-      <c r="N9" t="n">
-        <v>79.39540415975519</v>
-      </c>
-      <c r="O9" t="n">
-        <v>498.3699160492977</v>
-      </c>
-      <c r="P9" t="n">
-        <v>71.34613070725815</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>492.9061143040418</v>
-      </c>
       <c r="R9" t="n">
-        <v>68.93015632788671</v>
+        <v>479.62</v>
       </c>
       <c r="S9" t="n">
-        <v>489.4736780772171</v>
+        <v>77.06</v>
       </c>
       <c r="T9" t="n">
-        <v>66.85846778594063</v>
+        <v>486.64</v>
       </c>
       <c r="U9" t="n">
-        <v>487.7229761399116</v>
+        <v>64.37</v>
       </c>
       <c r="V9" t="n">
-        <v>64.15435926780256</v>
+        <v>491.27</v>
       </c>
       <c r="W9" t="n">
-        <v>490.7924466943635</v>
+        <v>69.98</v>
       </c>
       <c r="X9" t="n">
-        <v>61.58472132049192</v>
+        <v>489.71</v>
       </c>
       <c r="Y9" t="n">
-        <v>491.5648001131194</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="Z9" t="n">
-        <v>63.77838124428603</v>
+        <v>493.07</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>495.12</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>62.33</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>495.65</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>61.19</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>492.63</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>57.6</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>490.53</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>58.02</v>
       </c>
       <c r="AJ9" t="n">
-        <v>495.175</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>496.4</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>497.275</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>497.88</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>497.7833333333334</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>497.8714285714286</v>
+        <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>498.4625</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>499.6388888888889</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>499.65</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>68.0028997543487</v>
+        <v>499.775</v>
       </c>
       <c r="AT9" t="n">
-        <v>66.22718475067471</v>
+        <v>499.3333333333333</v>
       </c>
       <c r="AU9" t="n">
-        <v>78.32065101236073</v>
+        <v>499.875</v>
       </c>
       <c r="AV9" t="n">
-        <v>83.19762977393046</v>
+        <v>499.26</v>
       </c>
       <c r="AW9" t="n">
-        <v>80.30319455386289</v>
+        <v>500.8833333333333</v>
       </c>
       <c r="AX9" t="n">
-        <v>78.10239093259409</v>
+        <v>499.55</v>
       </c>
       <c r="AY9" t="n">
-        <v>76.01191415659785</v>
+        <v>499.51875</v>
       </c>
       <c r="AZ9" t="n">
-        <v>73.83327794496711</v>
+        <v>500.4611111111111</v>
       </c>
       <c r="BA9" t="n">
-        <v>73.95699764052081</v>
+        <v>500.19</v>
       </c>
       <c r="BB9" t="n">
-        <v>317</v>
+        <v>92.21943599372096</v>
       </c>
       <c r="BC9" t="n">
-        <v>317</v>
+        <v>86.11284586066252</v>
       </c>
       <c r="BD9" t="n">
-        <v>317</v>
+        <v>80.67610783249276</v>
       </c>
       <c r="BE9" t="n">
-        <v>317</v>
+        <v>74.20062263889704</v>
       </c>
       <c r="BF9" t="n">
-        <v>317</v>
+        <v>72.60064087565313</v>
       </c>
       <c r="BG9" t="n">
-        <v>317</v>
+        <v>70.01758197563156</v>
       </c>
       <c r="BH9" t="n">
-        <v>317</v>
+        <v>68.94136746857797</v>
       </c>
       <c r="BI9" t="n">
-        <v>317</v>
+        <v>67.9131278332751</v>
       </c>
       <c r="BJ9" t="n">
-        <v>317</v>
+        <v>67.14442568076669</v>
       </c>
       <c r="BK9" t="n">
-        <v>640</v>
+        <v>355</v>
       </c>
       <c r="BL9" t="n">
-        <v>640</v>
+        <v>355</v>
       </c>
       <c r="BM9" t="n">
-        <v>640</v>
+        <v>355</v>
       </c>
       <c r="BN9" t="n">
-        <v>640</v>
+        <v>355</v>
       </c>
       <c r="BO9" t="n">
-        <v>640</v>
+        <v>355</v>
       </c>
       <c r="BP9" t="n">
-        <v>640</v>
+        <v>355</v>
       </c>
       <c r="BQ9" t="n">
-        <v>640</v>
+        <v>355</v>
       </c>
       <c r="BR9" t="n">
-        <v>640</v>
+        <v>355</v>
       </c>
       <c r="BS9" t="n">
-        <v>640</v>
+        <v>355</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.75</v>
+        <v>669</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.5454545454545454</v>
+        <v>669</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.8181818181818182</v>
+        <v>669</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.9166666666666666</v>
+        <v>669</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.7647058823529411</v>
+        <v>669</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.7083333333333334</v>
+        <v>669</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.6666666666666666</v>
+        <v>669</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.7666666666666667</v>
+        <v>669</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0.8076923076923077</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0.7741935483870968</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>490.53</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>58.02</v>
       </c>
     </row>
     <row r="10">
@@ -2808,10 +3127,10 @@
         <v>500</v>
       </c>
       <c r="C10" t="n">
+        <v>90.43736100815418</v>
+      </c>
+      <c r="D10" t="n">
         <v>61</v>
-      </c>
-      <c r="D10" t="n">
-        <v>90.43736100815418</v>
       </c>
       <c r="E10" t="n">
         <v>500</v>
@@ -2820,228 +3139,261 @@
         <v>200</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H10" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>528.4012008705138</v>
-      </c>
-      <c r="J10" t="n">
-        <v>53.47188490694563</v>
-      </c>
-      <c r="K10" t="n">
-        <v>521.1649704201371</v>
-      </c>
-      <c r="L10" t="n">
-        <v>84.97274712440132</v>
-      </c>
-      <c r="M10" t="n">
-        <v>515.3885302330234</v>
-      </c>
-      <c r="N10" t="n">
-        <v>74.87696434770416</v>
-      </c>
-      <c r="O10" t="n">
-        <v>502.5058092809781</v>
-      </c>
-      <c r="P10" t="n">
-        <v>70.03818489212581</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>498.9542990949452</v>
-      </c>
       <c r="R10" t="n">
-        <v>66.05965091055315</v>
+        <v>528.4</v>
       </c>
       <c r="S10" t="n">
-        <v>500.7518108761928</v>
+        <v>53.47</v>
       </c>
       <c r="T10" t="n">
-        <v>62.70336010260129</v>
+        <v>521.16</v>
       </c>
       <c r="U10" t="n">
-        <v>497.3211597281667</v>
+        <v>84.97</v>
       </c>
       <c r="V10" t="n">
-        <v>63.83582679430447</v>
+        <v>515.39</v>
       </c>
       <c r="W10" t="n">
-        <v>502.2438967890597</v>
+        <v>74.88</v>
       </c>
       <c r="X10" t="n">
-        <v>64.61301491689674</v>
+        <v>502.51</v>
       </c>
       <c r="Y10" t="n">
-        <v>499.0630561301236</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="Z10" t="n">
-        <v>61.41930472226454</v>
+        <v>498.95</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>66.06</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>500.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>62.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>497.32</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>63.84</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>502.24</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>64.61</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>499.06</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>61.42</v>
       </c>
       <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
         <v>498.975</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AT10" t="n">
         <v>498.3</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AU10" t="n">
         <v>497.8</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AV10" t="n">
         <v>498.58</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AW10" t="n">
         <v>498.65</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AX10" t="n">
         <v>498.0571428571429</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AY10" t="n">
         <v>498.84375</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AZ10" t="n">
         <v>498.4833333333333</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="BA10" t="n">
         <v>498.79</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="BB10" t="n">
         <v>82.98719404221352</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="BC10" t="n">
         <v>79.72688797806337</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="BD10" t="n">
         <v>85.81279042194119</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="BE10" t="n">
         <v>86.49915375308593</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="BF10" t="n">
         <v>83.45044936967086</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="BG10" t="n">
         <v>79.75997666468453</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="BH10" t="n">
         <v>78.00789598455724</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BI10" t="n">
         <v>77.23078509679068</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BJ10" t="n">
         <v>74.78011700980416</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BK10" t="n">
         <v>338</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BL10" t="n">
         <v>338</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BM10" t="n">
         <v>338</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BN10" t="n">
         <v>338</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="BO10" t="n">
         <v>338</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BP10" t="n">
         <v>338</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BQ10" t="n">
         <v>338</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BR10" t="n">
         <v>338</v>
       </c>
-      <c r="BJ10" t="n">
+      <c r="BS10" t="n">
         <v>338</v>
       </c>
-      <c r="BK10" t="n">
+      <c r="BT10" t="n">
         <v>673</v>
       </c>
-      <c r="BL10" t="n">
+      <c r="BU10" t="n">
         <v>673</v>
       </c>
-      <c r="BM10" t="n">
+      <c r="BV10" t="n">
         <v>673</v>
       </c>
-      <c r="BN10" t="n">
+      <c r="BW10" t="n">
         <v>673</v>
       </c>
-      <c r="BO10" t="n">
+      <c r="BX10" t="n">
         <v>673</v>
       </c>
-      <c r="BP10" t="n">
+      <c r="BY10" t="n">
         <v>673</v>
       </c>
-      <c r="BQ10" t="n">
+      <c r="BZ10" t="n">
         <v>673</v>
       </c>
-      <c r="BR10" t="n">
+      <c r="CA10" t="n">
         <v>673</v>
       </c>
-      <c r="BS10" t="n">
+      <c r="CB10" t="n">
         <v>673</v>
       </c>
-      <c r="BT10" t="n">
+      <c r="CC10" t="n">
         <v>0.7692307692307693</v>
       </c>
-      <c r="BU10" t="n">
+      <c r="CD10" t="n">
         <v>0.7647058823529411</v>
       </c>
-      <c r="BV10" t="n">
+      <c r="CE10" t="n">
         <v>0.7647058823529411</v>
       </c>
-      <c r="BW10" t="n">
+      <c r="CF10" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="BX10" t="n">
+      <c r="CG10" t="n">
         <v>0.8421052631578947</v>
       </c>
-      <c r="BY10" t="n">
+      <c r="CH10" t="n">
         <v>0.8947368421052632</v>
       </c>
-      <c r="BZ10" t="n">
+      <c r="CI10" t="n">
         <v>0.9473684210526315</v>
       </c>
-      <c r="CA10" t="n">
+      <c r="CJ10" t="n">
         <v>1</v>
       </c>
-      <c r="CB10" t="n">
+      <c r="CK10" t="n">
         <v>0.9615384615384616</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>499.06</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>61.42</v>
       </c>
     </row>
     <row r="11">
@@ -3054,10 +3406,10 @@
         <v>501</v>
       </c>
       <c r="C11" t="n">
+        <v>85.9896219421794</v>
+      </c>
+      <c r="D11" t="n">
         <v>58</v>
-      </c>
-      <c r="D11" t="n">
-        <v>85.9896219421794</v>
       </c>
       <c r="E11" t="n">
         <v>501</v>
@@ -3066,228 +3418,261 @@
         <v>200</v>
       </c>
       <c r="G11" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="H11" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>591.796446815381</v>
-      </c>
-      <c r="J11" t="n">
-        <v>5.664497198787424</v>
-      </c>
-      <c r="K11" t="n">
-        <v>550.8639467348318</v>
-      </c>
-      <c r="L11" t="n">
-        <v>63.12778813659801</v>
-      </c>
-      <c r="M11" t="n">
-        <v>522.2575262900209</v>
-      </c>
-      <c r="N11" t="n">
-        <v>68.85867106405533</v>
-      </c>
-      <c r="O11" t="n">
-        <v>517.978002052773</v>
-      </c>
-      <c r="P11" t="n">
-        <v>68.85516888609581</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>513.4505598275429</v>
-      </c>
       <c r="R11" t="n">
-        <v>68.54959958185495</v>
+        <v>591.8</v>
       </c>
       <c r="S11" t="n">
-        <v>512.933269983581</v>
+        <v>5.66</v>
       </c>
       <c r="T11" t="n">
-        <v>73.00726309750259</v>
+        <v>550.86</v>
       </c>
       <c r="U11" t="n">
-        <v>512.1566790667263</v>
+        <v>63.13</v>
       </c>
       <c r="V11" t="n">
-        <v>76.81121392950017</v>
+        <v>522.26</v>
       </c>
       <c r="W11" t="n">
-        <v>518.6175935732207</v>
+        <v>68.86</v>
       </c>
       <c r="X11" t="n">
-        <v>79.7753394228552</v>
+        <v>517.98</v>
       </c>
       <c r="Y11" t="n">
-        <v>511.8930233618199</v>
+        <v>68.86</v>
       </c>
       <c r="Z11" t="n">
-        <v>79.86287693759415</v>
+        <v>513.45</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>68.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>512.9299999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>512.16</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>76.81</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>518.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>79.78</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>511.89</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>79.86</v>
       </c>
       <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
         <v>498.3</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AT11" t="n">
         <v>498.8333333333333</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AU11" t="n">
         <v>499.5</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AV11" t="n">
         <v>498.41</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AW11" t="n">
         <v>497.1</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AX11" t="n">
         <v>498.8642857142857</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AY11" t="n">
         <v>498.8</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AZ11" t="n">
         <v>498.05</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="BA11" t="n">
         <v>497.1</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="BB11" t="n">
         <v>102.4795589373803</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="BC11" t="n">
         <v>92.36055555388471</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="BD11" t="n">
         <v>85.66227290937358</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="BE11" t="n">
         <v>78.57774430460576</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="BF11" t="n">
         <v>80.63522803340982</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="BG11" t="n">
         <v>80.42860282922503</v>
       </c>
-      <c r="AY11" t="n">
+      <c r="BH11" t="n">
         <v>88.50542356262694</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BI11" t="n">
         <v>91.86174847744479</v>
       </c>
-      <c r="BA11" t="n">
+      <c r="BJ11" t="n">
         <v>92.36016457326177</v>
       </c>
-      <c r="BB11" t="n">
+      <c r="BK11" t="n">
         <v>334</v>
       </c>
-      <c r="BC11" t="n">
+      <c r="BL11" t="n">
         <v>334</v>
       </c>
-      <c r="BD11" t="n">
+      <c r="BM11" t="n">
         <v>334</v>
       </c>
-      <c r="BE11" t="n">
+      <c r="BN11" t="n">
         <v>334</v>
       </c>
-      <c r="BF11" t="n">
+      <c r="BO11" t="n">
         <v>334</v>
       </c>
-      <c r="BG11" t="n">
+      <c r="BP11" t="n">
         <v>334</v>
       </c>
-      <c r="BH11" t="n">
+      <c r="BQ11" t="n">
         <v>334</v>
       </c>
-      <c r="BI11" t="n">
+      <c r="BR11" t="n">
         <v>334</v>
       </c>
-      <c r="BJ11" t="n">
+      <c r="BS11" t="n">
         <v>334</v>
       </c>
-      <c r="BK11" t="n">
+      <c r="BT11" t="n">
         <v>640</v>
       </c>
-      <c r="BL11" t="n">
+      <c r="BU11" t="n">
         <v>640</v>
       </c>
-      <c r="BM11" t="n">
+      <c r="BV11" t="n">
         <v>640</v>
       </c>
-      <c r="BN11" t="n">
+      <c r="BW11" t="n">
         <v>640</v>
       </c>
-      <c r="BO11" t="n">
+      <c r="BX11" t="n">
         <v>640</v>
       </c>
-      <c r="BP11" t="n">
+      <c r="BY11" t="n">
         <v>640</v>
       </c>
-      <c r="BQ11" t="n">
+      <c r="BZ11" t="n">
         <v>642</v>
       </c>
-      <c r="BR11" t="n">
+      <c r="CA11" t="n">
         <v>642</v>
       </c>
-      <c r="BS11" t="n">
+      <c r="CB11" t="n">
         <v>642</v>
       </c>
-      <c r="BT11" t="n">
+      <c r="CC11" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="BU11" t="n">
+      <c r="CD11" t="n">
         <v>1</v>
       </c>
-      <c r="BV11" t="n">
+      <c r="CE11" t="n">
         <v>0.75</v>
       </c>
-      <c r="BW11" t="n">
+      <c r="CF11" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BX11" t="n">
+      <c r="CG11" t="n">
         <v>0.8125</v>
       </c>
-      <c r="BY11" t="n">
+      <c r="CH11" t="n">
         <v>0.7</v>
       </c>
-      <c r="BZ11" t="n">
+      <c r="CI11" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="CA11" t="n">
+      <c r="CJ11" t="n">
         <v>0.6</v>
       </c>
-      <c r="CB11" t="n">
+      <c r="CK11" t="n">
         <v>0.6206896551724138</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>511.89</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>79.86</v>
       </c>
     </row>
     <row r="12">
@@ -3300,10 +3685,10 @@
         <v>499</v>
       </c>
       <c r="C12" t="n">
+        <v>85.9896219421794</v>
+      </c>
+      <c r="D12" t="n">
         <v>58</v>
-      </c>
-      <c r="D12" t="n">
-        <v>85.9896219421794</v>
       </c>
       <c r="E12" t="n">
         <v>499</v>
@@ -3312,228 +3697,261 @@
         <v>200</v>
       </c>
       <c r="G12" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H12" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>522.1679190820283</v>
-      </c>
-      <c r="J12" t="n">
-        <v>71.39651565948127</v>
-      </c>
-      <c r="K12" t="n">
-        <v>512.0575404105487</v>
-      </c>
-      <c r="L12" t="n">
-        <v>61.45816745768961</v>
-      </c>
-      <c r="M12" t="n">
-        <v>530.1402437929413</v>
-      </c>
-      <c r="N12" t="n">
-        <v>59.11610017294126</v>
-      </c>
-      <c r="O12" t="n">
-        <v>522.3217179333153</v>
-      </c>
-      <c r="P12" t="n">
-        <v>55.66086308369486</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>516.6757413844939</v>
-      </c>
       <c r="R12" t="n">
-        <v>58.15385914167818</v>
+        <v>522.17</v>
       </c>
       <c r="S12" t="n">
-        <v>512.9814344633591</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>58.69860491437618</v>
+        <v>512.0599999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>509.6237454803619</v>
+        <v>61.46</v>
       </c>
       <c r="V12" t="n">
-        <v>57.39256660825153</v>
+        <v>530.14</v>
       </c>
       <c r="W12" t="n">
-        <v>511.3816649224832</v>
+        <v>59.12</v>
       </c>
       <c r="X12" t="n">
-        <v>55.98099784158486</v>
+        <v>522.3200000000001</v>
       </c>
       <c r="Y12" t="n">
-        <v>509.5745701132577</v>
+        <v>55.66</v>
       </c>
       <c r="Z12" t="n">
-        <v>54.1394669567075</v>
+        <v>516.6799999999999</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>58.15</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>512.98</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>58.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>509.62</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>57.39</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>511.38</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>55.98</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>509.57</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>54.14</v>
       </c>
       <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
         <v>499.275</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AT12" t="n">
         <v>498.7333333333333</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AU12" t="n">
         <v>498.1875</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AV12" t="n">
         <v>498.18</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AW12" t="n">
         <v>498.1416666666667</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AX12" t="n">
         <v>498.2142857142857</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AY12" t="n">
         <v>499.05625</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AZ12" t="n">
         <v>498.15</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="BA12" t="n">
         <v>496.835</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="BB12" t="n">
         <v>106.3371965729772</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="BC12" t="n">
         <v>95.22409825715805</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="BD12" t="n">
         <v>88.86704869494655</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="BE12" t="n">
         <v>83.96194137822209</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="BF12" t="n">
         <v>79.05138580203527</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="BG12" t="n">
         <v>74.39679195409721</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="BH12" t="n">
         <v>71.00486311470152</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BI12" t="n">
         <v>67.87034002828891</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BJ12" t="n">
         <v>66.35636951340844</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BK12" t="n">
         <v>340</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BL12" t="n">
         <v>340</v>
       </c>
-      <c r="BD12" t="n">
+      <c r="BM12" t="n">
         <v>340</v>
       </c>
-      <c r="BE12" t="n">
+      <c r="BN12" t="n">
         <v>340</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="BO12" t="n">
         <v>340</v>
       </c>
-      <c r="BG12" t="n">
+      <c r="BP12" t="n">
         <v>340</v>
       </c>
-      <c r="BH12" t="n">
+      <c r="BQ12" t="n">
         <v>340</v>
       </c>
-      <c r="BI12" t="n">
+      <c r="BR12" t="n">
         <v>340</v>
       </c>
-      <c r="BJ12" t="n">
+      <c r="BS12" t="n">
         <v>340</v>
       </c>
-      <c r="BK12" t="n">
+      <c r="BT12" t="n">
         <v>673</v>
       </c>
-      <c r="BL12" t="n">
+      <c r="BU12" t="n">
         <v>673</v>
       </c>
-      <c r="BM12" t="n">
+      <c r="BV12" t="n">
         <v>673</v>
       </c>
-      <c r="BN12" t="n">
+      <c r="BW12" t="n">
         <v>673</v>
       </c>
-      <c r="BO12" t="n">
+      <c r="BX12" t="n">
         <v>673</v>
       </c>
-      <c r="BP12" t="n">
+      <c r="BY12" t="n">
         <v>673</v>
       </c>
-      <c r="BQ12" t="n">
+      <c r="BZ12" t="n">
         <v>673</v>
       </c>
-      <c r="BR12" t="n">
+      <c r="CA12" t="n">
         <v>673</v>
       </c>
-      <c r="BS12" t="n">
+      <c r="CB12" t="n">
         <v>673</v>
       </c>
-      <c r="BT12" t="n">
+      <c r="CC12" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BU12" t="n">
+      <c r="CD12" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="BV12" t="n">
+      <c r="CE12" t="n">
         <v>0.9</v>
       </c>
-      <c r="BW12" t="n">
+      <c r="CF12" t="n">
         <v>1</v>
       </c>
-      <c r="BX12" t="n">
+      <c r="CG12" t="n">
         <v>0.9615384615384616</v>
       </c>
-      <c r="BY12" t="n">
+      <c r="CH12" t="n">
         <v>0.9615384615384616</v>
       </c>
-      <c r="BZ12" t="n">
+      <c r="CI12" t="n">
         <v>0.9615384615384616</v>
       </c>
-      <c r="CA12" t="n">
+      <c r="CJ12" t="n">
         <v>0.9615384615384616</v>
       </c>
-      <c r="CB12" t="n">
+      <c r="CK12" t="n">
         <v>0.9615384615384616</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>509.57</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>54.14</v>
       </c>
     </row>
     <row r="13">
@@ -3546,10 +3964,10 @@
         <v>498</v>
       </c>
       <c r="C13" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D13" t="n">
         <v>60</v>
-      </c>
-      <c r="D13" t="n">
-        <v>88.95478131949592</v>
       </c>
       <c r="E13" t="n">
         <v>498</v>
@@ -3558,228 +3976,261 @@
         <v>200</v>
       </c>
       <c r="G13" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="H13" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>508.3555493020858</v>
-      </c>
-      <c r="J13" t="n">
-        <v>51.62243991096344</v>
-      </c>
-      <c r="K13" t="n">
-        <v>509.5384559354015</v>
-      </c>
-      <c r="L13" t="n">
-        <v>54.53508076319032</v>
-      </c>
-      <c r="M13" t="n">
-        <v>484.7263608115703</v>
-      </c>
-      <c r="N13" t="n">
-        <v>68.99329189178492</v>
-      </c>
-      <c r="O13" t="n">
-        <v>490.1572909324525</v>
-      </c>
-      <c r="P13" t="n">
-        <v>77.85174291927612</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>488.0078366387535</v>
-      </c>
       <c r="R13" t="n">
-        <v>80.12761734794684</v>
+        <v>508.36</v>
       </c>
       <c r="S13" t="n">
-        <v>486.9938406039576</v>
+        <v>51.62</v>
       </c>
       <c r="T13" t="n">
-        <v>79.66183789814501</v>
+        <v>509.54</v>
       </c>
       <c r="U13" t="n">
-        <v>485.6739118289796</v>
+        <v>54.54</v>
       </c>
       <c r="V13" t="n">
-        <v>79.32914918094041</v>
+        <v>484.73</v>
       </c>
       <c r="W13" t="n">
-        <v>486.6753455900357</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>75.54467487927349</v>
+        <v>490.16</v>
       </c>
       <c r="Y13" t="n">
-        <v>486.2332602216038</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="Z13" t="n">
-        <v>73.02933016462767</v>
+        <v>488.01</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>80.13</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>486.99</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>79.66</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>485.67</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>79.33</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>486.68</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>486.23</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>73.03</v>
       </c>
       <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
         <v>499.175</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AT13" t="n">
         <v>499.2166666666666</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AU13" t="n">
         <v>499.975</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AV13" t="n">
         <v>500.13</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AW13" t="n">
         <v>499.9583333333333</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AX13" t="n">
         <v>500.2285714285715</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AY13" t="n">
         <v>499.475</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AZ13" t="n">
         <v>498.5166666666667</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="BA13" t="n">
         <v>498.145</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="BB13" t="n">
         <v>87.95336477361171</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="BC13" t="n">
         <v>77.87812950729848</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="BD13" t="n">
         <v>72.47050693213068</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="BE13" t="n">
         <v>76.25085638863342</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="BF13" t="n">
         <v>85.24380679687071</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="BG13" t="n">
         <v>89.72078456898085</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="BH13" t="n">
         <v>89.9566527556467</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="BI13" t="n">
         <v>88.18814955662819</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BJ13" t="n">
         <v>86.27655518737404</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BK13" t="n">
         <v>358</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BL13" t="n">
         <v>358</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BM13" t="n">
         <v>358</v>
       </c>
-      <c r="BE13" t="n">
+      <c r="BN13" t="n">
         <v>358</v>
       </c>
-      <c r="BF13" t="n">
+      <c r="BO13" t="n">
         <v>358</v>
       </c>
-      <c r="BG13" t="n">
+      <c r="BP13" t="n">
         <v>358</v>
       </c>
-      <c r="BH13" t="n">
+      <c r="BQ13" t="n">
         <v>358</v>
       </c>
-      <c r="BI13" t="n">
+      <c r="BR13" t="n">
         <v>358</v>
       </c>
-      <c r="BJ13" t="n">
+      <c r="BS13" t="n">
         <v>358</v>
       </c>
-      <c r="BK13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>669</v>
-      </c>
       <c r="BT13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC13" t="n">
         <v>0.6</v>
       </c>
-      <c r="BU13" t="n">
+      <c r="CD13" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="BV13" t="n">
+      <c r="CE13" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="BW13" t="n">
+      <c r="CF13" t="n">
         <v>0.631578947368421</v>
       </c>
-      <c r="BX13" t="n">
+      <c r="CG13" t="n">
         <v>0.6842105263157895</v>
       </c>
-      <c r="BY13" t="n">
+      <c r="CH13" t="n">
         <v>0.8947368421052632</v>
       </c>
-      <c r="BZ13" t="n">
+      <c r="CI13" t="n">
         <v>0.8947368421052632</v>
       </c>
-      <c r="CA13" t="n">
+      <c r="CJ13" t="n">
         <v>0.8947368421052632</v>
       </c>
-      <c r="CB13" t="n">
+      <c r="CK13" t="n">
         <v>0.9473684210526315</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>486.23</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>73.03</v>
       </c>
     </row>
     <row r="14">
@@ -3792,10 +4243,10 @@
         <v>499</v>
       </c>
       <c r="C14" t="n">
+        <v>85.9896219421794</v>
+      </c>
+      <c r="D14" t="n">
         <v>58</v>
-      </c>
-      <c r="D14" t="n">
-        <v>85.9896219421794</v>
       </c>
       <c r="E14" t="n">
         <v>499</v>
@@ -3804,228 +4255,261 @@
         <v>200</v>
       </c>
       <c r="G14" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="H14" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>485.3021979733473</v>
-      </c>
-      <c r="J14" t="n">
-        <v>65.27882958251762</v>
-      </c>
-      <c r="K14" t="n">
-        <v>453.9536922405929</v>
-      </c>
-      <c r="L14" t="n">
-        <v>73.47614229091577</v>
-      </c>
-      <c r="M14" t="n">
-        <v>463.3180588253385</v>
-      </c>
-      <c r="N14" t="n">
-        <v>72.44273972935575</v>
-      </c>
-      <c r="O14" t="n">
-        <v>478.8460254427497</v>
-      </c>
-      <c r="P14" t="n">
-        <v>77.34157588726313</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>489.5991109018253</v>
-      </c>
       <c r="R14" t="n">
-        <v>76.86703571037636</v>
+        <v>485.3</v>
       </c>
       <c r="S14" t="n">
-        <v>484.1008206907335</v>
+        <v>65.28</v>
       </c>
       <c r="T14" t="n">
-        <v>71.77360817948656</v>
+        <v>453.95</v>
       </c>
       <c r="U14" t="n">
-        <v>484.8912770974831</v>
+        <v>73.48</v>
       </c>
       <c r="V14" t="n">
-        <v>70.54765034117789</v>
+        <v>463.32</v>
       </c>
       <c r="W14" t="n">
-        <v>486.3078506500891</v>
+        <v>72.44</v>
       </c>
       <c r="X14" t="n">
-        <v>72.15554650904322</v>
+        <v>478.85</v>
       </c>
       <c r="Y14" t="n">
-        <v>485.6880224294795</v>
+        <v>77.34</v>
       </c>
       <c r="Z14" t="n">
-        <v>72.18858822587849</v>
+        <v>489.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>76.87</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>484.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>71.77</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>484.89</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>70.55</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>486.31</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>72.16</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>485.69</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>72.19</v>
       </c>
       <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
         <v>501.05</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AT14" t="n">
         <v>501.2</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AU14" t="n">
         <v>500.75</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AV14" t="n">
         <v>497.81</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AW14" t="n">
         <v>498.2916666666667</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AX14" t="n">
         <v>495.7571428571429</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="AY14" t="n">
         <v>499.1125</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AZ14" t="n">
         <v>499.1277777777778</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="BA14" t="n">
         <v>499.16</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="BB14" t="n">
         <v>80.15764155712168</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="BC14" t="n">
         <v>84.40572650399181</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="BD14" t="n">
         <v>90.4844599917577</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="BE14" t="n">
         <v>91.9641990124418</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="BF14" t="n">
         <v>86.27546926689082</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="BG14" t="n">
         <v>83.07559994440274</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="BH14" t="n">
         <v>82.64109052856213</v>
       </c>
-      <c r="AZ14" t="n">
+      <c r="BI14" t="n">
         <v>83.20984387248873</v>
       </c>
-      <c r="BA14" t="n">
+      <c r="BJ14" t="n">
         <v>85.01137806199826</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BK14" t="n">
         <v>330</v>
       </c>
-      <c r="BC14" t="n">
+      <c r="BL14" t="n">
         <v>330</v>
       </c>
-      <c r="BD14" t="n">
+      <c r="BM14" t="n">
         <v>330</v>
       </c>
-      <c r="BE14" t="n">
+      <c r="BN14" t="n">
         <v>330</v>
       </c>
-      <c r="BF14" t="n">
+      <c r="BO14" t="n">
         <v>330</v>
       </c>
-      <c r="BG14" t="n">
+      <c r="BP14" t="n">
         <v>330</v>
       </c>
-      <c r="BH14" t="n">
+      <c r="BQ14" t="n">
         <v>330</v>
       </c>
-      <c r="BI14" t="n">
+      <c r="BR14" t="n">
         <v>330</v>
       </c>
-      <c r="BJ14" t="n">
+      <c r="BS14" t="n">
         <v>330</v>
       </c>
-      <c r="BK14" t="n">
+      <c r="BT14" t="n">
         <v>637</v>
       </c>
-      <c r="BL14" t="n">
+      <c r="BU14" t="n">
         <v>637</v>
       </c>
-      <c r="BM14" t="n">
+      <c r="BV14" t="n">
         <v>637</v>
       </c>
-      <c r="BN14" t="n">
+      <c r="BW14" t="n">
         <v>637</v>
       </c>
-      <c r="BO14" t="n">
+      <c r="BX14" t="n">
         <v>637</v>
       </c>
-      <c r="BP14" t="n">
+      <c r="BY14" t="n">
         <v>637</v>
       </c>
-      <c r="BQ14" t="n">
+      <c r="BZ14" t="n">
         <v>637</v>
       </c>
-      <c r="BR14" t="n">
+      <c r="CA14" t="n">
         <v>637</v>
       </c>
-      <c r="BS14" t="n">
+      <c r="CB14" t="n">
         <v>637</v>
       </c>
-      <c r="BT14" t="n">
+      <c r="CC14" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="BU14" t="n">
+      <c r="CD14" t="n">
         <v>0.3571428571428572</v>
       </c>
-      <c r="BV14" t="n">
+      <c r="CE14" t="n">
         <v>0.6428571428571429</v>
       </c>
-      <c r="BW14" t="n">
+      <c r="CF14" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BX14" t="n">
+      <c r="CG14" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BY14" t="n">
+      <c r="CH14" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="BZ14" t="n">
+      <c r="CI14" t="n">
         <v>0.8947368421052632</v>
       </c>
-      <c r="CA14" t="n">
+      <c r="CJ14" t="n">
         <v>1</v>
       </c>
-      <c r="CB14" t="n">
+      <c r="CK14" t="n">
         <v>0.8846153846153846</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>485.69</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>72.19</v>
       </c>
     </row>
     <row r="15">
@@ -4038,10 +4522,10 @@
         <v>500</v>
       </c>
       <c r="C15" t="n">
+        <v>90.43736100815418</v>
+      </c>
+      <c r="D15" t="n">
         <v>61</v>
-      </c>
-      <c r="D15" t="n">
-        <v>90.43736100815418</v>
       </c>
       <c r="E15" t="n">
         <v>500</v>
@@ -4050,228 +4534,261 @@
         <v>200</v>
       </c>
       <c r="G15" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="H15" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>501.9520932404537</v>
-      </c>
-      <c r="J15" t="n">
-        <v>52.14849555639228</v>
-      </c>
-      <c r="K15" t="n">
-        <v>494.4880306563061</v>
-      </c>
-      <c r="L15" t="n">
-        <v>73.11448373542181</v>
-      </c>
-      <c r="M15" t="n">
-        <v>496.5212472641537</v>
-      </c>
-      <c r="N15" t="n">
-        <v>62.89299958945471</v>
-      </c>
-      <c r="O15" t="n">
-        <v>501.5212355212908</v>
-      </c>
-      <c r="P15" t="n">
-        <v>57.85707956125736</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>504.8114172451258</v>
-      </c>
       <c r="R15" t="n">
-        <v>61.54298067489295</v>
+        <v>501.95</v>
       </c>
       <c r="S15" t="n">
-        <v>497.365893816122</v>
+        <v>52.15</v>
       </c>
       <c r="T15" t="n">
-        <v>59.81851156046486</v>
+        <v>494.49</v>
       </c>
       <c r="U15" t="n">
-        <v>497.5378474331395</v>
+        <v>73.11</v>
       </c>
       <c r="V15" t="n">
-        <v>59.47794433899161</v>
+        <v>496.52</v>
       </c>
       <c r="W15" t="n">
-        <v>496.4471602861225</v>
+        <v>62.89</v>
       </c>
       <c r="X15" t="n">
-        <v>57.57020704810265</v>
+        <v>501.52</v>
       </c>
       <c r="Y15" t="n">
-        <v>489.9962504547927</v>
+        <v>57.86</v>
       </c>
       <c r="Z15" t="n">
-        <v>59.66473856441036</v>
+        <v>504.81</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>61.54</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>497.37</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>59.82</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>497.54</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>59.48</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>496.45</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>57.57</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>490</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>59.66</v>
       </c>
       <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
         <v>500.725</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AT15" t="n">
         <v>499.9666666666666</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AU15" t="n">
         <v>500.0625</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AV15" t="n">
         <v>501.06</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AW15" t="n">
         <v>502.0666666666667</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AX15" t="n">
         <v>502.95</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AY15" t="n">
         <v>502.5375</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AZ15" t="n">
         <v>502.2611111111111</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="BA15" t="n">
         <v>502.18</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="BB15" t="n">
         <v>90.70115420985556</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="BC15" t="n">
         <v>82.36665317685038</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="BD15" t="n">
         <v>77.18716599118017</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="BE15" t="n">
         <v>73.95726063071834</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="BF15" t="n">
         <v>69.14088676190248</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="BG15" t="n">
         <v>68.13393584907388</v>
       </c>
-      <c r="AY15" t="n">
+      <c r="BH15" t="n">
         <v>68.59399458954114</v>
       </c>
-      <c r="AZ15" t="n">
+      <c r="BI15" t="n">
         <v>67.47661025939851</v>
       </c>
-      <c r="BA15" t="n">
+      <c r="BJ15" t="n">
         <v>68.25201535485967</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BK15" t="n">
         <v>331</v>
       </c>
-      <c r="BC15" t="n">
+      <c r="BL15" t="n">
         <v>331</v>
       </c>
-      <c r="BD15" t="n">
+      <c r="BM15" t="n">
         <v>331</v>
       </c>
-      <c r="BE15" t="n">
+      <c r="BN15" t="n">
         <v>331</v>
       </c>
-      <c r="BF15" t="n">
+      <c r="BO15" t="n">
         <v>331</v>
       </c>
-      <c r="BG15" t="n">
+      <c r="BP15" t="n">
         <v>331</v>
       </c>
-      <c r="BH15" t="n">
+      <c r="BQ15" t="n">
         <v>331</v>
       </c>
-      <c r="BI15" t="n">
+      <c r="BR15" t="n">
         <v>331</v>
       </c>
-      <c r="BJ15" t="n">
+      <c r="BS15" t="n">
         <v>331</v>
       </c>
-      <c r="BK15" t="n">
+      <c r="BT15" t="n">
         <v>637</v>
       </c>
-      <c r="BL15" t="n">
+      <c r="BU15" t="n">
         <v>637</v>
       </c>
-      <c r="BM15" t="n">
+      <c r="BV15" t="n">
         <v>637</v>
       </c>
-      <c r="BN15" t="n">
+      <c r="BW15" t="n">
         <v>637</v>
       </c>
-      <c r="BO15" t="n">
+      <c r="BX15" t="n">
         <v>637</v>
       </c>
-      <c r="BP15" t="n">
+      <c r="BY15" t="n">
         <v>637</v>
       </c>
-      <c r="BQ15" t="n">
+      <c r="BZ15" t="n">
         <v>637</v>
       </c>
-      <c r="BR15" t="n">
+      <c r="CA15" t="n">
         <v>637</v>
       </c>
-      <c r="BS15" t="n">
+      <c r="CB15" t="n">
         <v>637</v>
       </c>
-      <c r="BT15" t="n">
+      <c r="CC15" t="n">
         <v>0.875</v>
       </c>
-      <c r="BU15" t="n">
+      <c r="CD15" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="BV15" t="n">
+      <c r="CE15" t="n">
         <v>0.7857142857142857</v>
       </c>
-      <c r="BW15" t="n">
+      <c r="CF15" t="n">
         <v>0.7857142857142857</v>
       </c>
-      <c r="BX15" t="n">
+      <c r="CG15" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="BY15" t="n">
+      <c r="CH15" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="BZ15" t="n">
+      <c r="CI15" t="n">
         <v>0.9375</v>
       </c>
-      <c r="CA15" t="n">
+      <c r="CJ15" t="n">
         <v>0.9473684210526315</v>
       </c>
-      <c r="CB15" t="n">
+      <c r="CK15" t="n">
         <v>0.8636363636363636</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>490</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>59.66</v>
       </c>
     </row>
     <row r="16">
@@ -4284,10 +4801,10 @@
         <v>501</v>
       </c>
       <c r="C16" t="n">
+        <v>85.9896219421794</v>
+      </c>
+      <c r="D16" t="n">
         <v>58</v>
-      </c>
-      <c r="D16" t="n">
-        <v>85.9896219421794</v>
       </c>
       <c r="E16" t="n">
         <v>501</v>
@@ -4296,228 +4813,261 @@
         <v>200</v>
       </c>
       <c r="G16" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="H16" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>497.2110400384518</v>
-      </c>
-      <c r="J16" t="n">
-        <v>76.55301885037842</v>
-      </c>
-      <c r="K16" t="n">
-        <v>493.4075298669308</v>
-      </c>
-      <c r="L16" t="n">
-        <v>69.25911895206147</v>
-      </c>
-      <c r="M16" t="n">
-        <v>490.9789743815365</v>
-      </c>
-      <c r="N16" t="n">
-        <v>69.84510809250203</v>
-      </c>
-      <c r="O16" t="n">
-        <v>499.0283179467841</v>
-      </c>
-      <c r="P16" t="n">
-        <v>69.66766685026549</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>496.6200495626355</v>
-      </c>
       <c r="R16" t="n">
-        <v>64.2394552449807</v>
+        <v>497.21</v>
       </c>
       <c r="S16" t="n">
-        <v>492.0984423108088</v>
+        <v>76.55</v>
       </c>
       <c r="T16" t="n">
-        <v>71.32270292598784</v>
+        <v>493.41</v>
       </c>
       <c r="U16" t="n">
-        <v>490.7540421427897</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>71.3071070107946</v>
+        <v>490.98</v>
       </c>
       <c r="W16" t="n">
-        <v>490.1708527385069</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>65.19608299141977</v>
+        <v>499.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>491.8037391992793</v>
+        <v>69.67</v>
       </c>
       <c r="Z16" t="n">
-        <v>66.03360510552511</v>
+        <v>496.62</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>492.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>490.75</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>71.31</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>490.17</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>65.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>491.8</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>66.03</v>
       </c>
       <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
         <v>495.6</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AT16" t="n">
         <v>497.6833333333333</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AU16" t="n">
         <v>498.1375</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AV16" t="n">
         <v>498.24</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AW16" t="n">
         <v>498.4833333333333</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="AX16" t="n">
         <v>498.2928571428571</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AY16" t="n">
         <v>498.38125</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AZ16" t="n">
         <v>498.2444444444445</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="BA16" t="n">
         <v>498.625</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="BB16" t="n">
         <v>77.43248672230538</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="BC16" t="n">
         <v>77.49655727120327</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="BD16" t="n">
         <v>74.88420122929803</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="BE16" t="n">
         <v>74.83944414545047</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="BF16" t="n">
         <v>72.45055593682878</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="BG16" t="n">
         <v>71.44013442122326</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="BH16" t="n">
         <v>74.35109883813082</v>
       </c>
-      <c r="AZ16" t="n">
+      <c r="BI16" t="n">
         <v>73.04379372998869</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BJ16" t="n">
         <v>70.05914911701397</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BK16" t="n">
         <v>327</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BL16" t="n">
         <v>327</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BM16" t="n">
         <v>327</v>
       </c>
-      <c r="BE16" t="n">
+      <c r="BN16" t="n">
         <v>327</v>
       </c>
-      <c r="BF16" t="n">
+      <c r="BO16" t="n">
         <v>327</v>
       </c>
-      <c r="BG16" t="n">
+      <c r="BP16" t="n">
         <v>327</v>
       </c>
-      <c r="BH16" t="n">
+      <c r="BQ16" t="n">
         <v>327</v>
       </c>
-      <c r="BI16" t="n">
+      <c r="BR16" t="n">
         <v>327</v>
       </c>
-      <c r="BJ16" t="n">
+      <c r="BS16" t="n">
         <v>327</v>
       </c>
-      <c r="BK16" t="n">
+      <c r="BT16" t="n">
         <v>612</v>
       </c>
-      <c r="BL16" t="n">
+      <c r="BU16" t="n">
         <v>612</v>
       </c>
-      <c r="BM16" t="n">
+      <c r="BV16" t="n">
         <v>612</v>
       </c>
-      <c r="BN16" t="n">
+      <c r="BW16" t="n">
         <v>612</v>
       </c>
-      <c r="BO16" t="n">
+      <c r="BX16" t="n">
         <v>612</v>
       </c>
-      <c r="BP16" t="n">
+      <c r="BY16" t="n">
         <v>612</v>
       </c>
-      <c r="BQ16" t="n">
+      <c r="BZ16" t="n">
         <v>612</v>
       </c>
-      <c r="BR16" t="n">
+      <c r="CA16" t="n">
         <v>612</v>
       </c>
-      <c r="BS16" t="n">
+      <c r="CB16" t="n">
         <v>612</v>
       </c>
-      <c r="BT16" t="n">
+      <c r="CC16" t="n">
         <v>0.8</v>
       </c>
-      <c r="BU16" t="n">
+      <c r="CD16" t="n">
         <v>0.75</v>
       </c>
-      <c r="BV16" t="n">
+      <c r="CE16" t="n">
         <v>0.9444444444444444</v>
       </c>
-      <c r="BW16" t="n">
+      <c r="CF16" t="n">
         <v>0.9130434782608695</v>
       </c>
-      <c r="BX16" t="n">
+      <c r="CG16" t="n">
         <v>0.9629629629629629</v>
       </c>
-      <c r="BY16" t="n">
+      <c r="CH16" t="n">
         <v>0.03703703703703703</v>
       </c>
-      <c r="BZ16" t="n">
+      <c r="CI16" t="n">
         <v>0.9642857142857143</v>
       </c>
-      <c r="CA16" t="n">
+      <c r="CJ16" t="n">
         <v>0.9642857142857143</v>
       </c>
-      <c r="CB16" t="n">
+      <c r="CK16" t="n">
         <v>0.9642857142857143</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>491.8</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>66.03</v>
       </c>
     </row>
     <row r="17">
@@ -4530,10 +5080,10 @@
         <v>500</v>
       </c>
       <c r="C17" t="n">
+        <v>87.47220163083766</v>
+      </c>
+      <c r="D17" t="n">
         <v>59</v>
-      </c>
-      <c r="D17" t="n">
-        <v>87.47220163083766</v>
       </c>
       <c r="E17" t="n">
         <v>500</v>
@@ -4542,228 +5092,261 @@
         <v>200</v>
       </c>
       <c r="G17" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="H17" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>465.1515118771121</v>
-      </c>
-      <c r="J17" t="n">
-        <v>58.10777227823252</v>
-      </c>
-      <c r="K17" t="n">
-        <v>462.6136033044229</v>
-      </c>
-      <c r="L17" t="n">
-        <v>67.61010667332523</v>
-      </c>
-      <c r="M17" t="n">
-        <v>477.3147354307866</v>
-      </c>
-      <c r="N17" t="n">
-        <v>66.12056381704519</v>
-      </c>
-      <c r="O17" t="n">
-        <v>472.7442114874268</v>
-      </c>
-      <c r="P17" t="n">
-        <v>70.10278730176117</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>489.0840416259392</v>
-      </c>
       <c r="R17" t="n">
-        <v>73.18129823009694</v>
+        <v>465.15</v>
       </c>
       <c r="S17" t="n">
-        <v>488.4663759418724</v>
+        <v>58.11</v>
       </c>
       <c r="T17" t="n">
-        <v>71.24835085964408</v>
+        <v>462.61</v>
       </c>
       <c r="U17" t="n">
-        <v>487.1343346469249</v>
+        <v>67.61</v>
       </c>
       <c r="V17" t="n">
-        <v>70.20320836571385</v>
+        <v>477.31</v>
       </c>
       <c r="W17" t="n">
-        <v>493.2770521020297</v>
+        <v>66.12</v>
       </c>
       <c r="X17" t="n">
-        <v>72.05364047263082</v>
+        <v>472.74</v>
       </c>
       <c r="Y17" t="n">
-        <v>488.9776670660217</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="Z17" t="n">
-        <v>73.0031520403797</v>
+        <v>489.08</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>488.47</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>71.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>487.13</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>70.2</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>493.28</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>72.05</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>488.98</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
         <v>498.55</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AT17" t="n">
         <v>499.2333333333333</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AU17" t="n">
         <v>499.15</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="AV17" t="n">
         <v>499.85</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="AW17" t="n">
         <v>500.2083333333333</v>
       </c>
-      <c r="AO17" t="n">
+      <c r="AX17" t="n">
         <v>500.6357142857143</v>
       </c>
-      <c r="AP17" t="n">
+      <c r="AY17" t="n">
         <v>501.23125</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AZ17" t="n">
         <v>500.3777777777778</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="BA17" t="n">
         <v>500.545</v>
       </c>
-      <c r="AS17" t="n">
+      <c r="BB17" t="n">
         <v>105.9610659629281</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="BC17" t="n">
         <v>93.541321825645</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="BD17" t="n">
         <v>88.40207859547195</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="BE17" t="n">
         <v>84.3602246322282</v>
       </c>
-      <c r="AW17" t="n">
+      <c r="BF17" t="n">
         <v>82.86604610588236</v>
       </c>
-      <c r="AX17" t="n">
+      <c r="BG17" t="n">
         <v>84.09681586585494</v>
       </c>
-      <c r="AY17" t="n">
+      <c r="BH17" t="n">
         <v>80.11220427274175</v>
       </c>
-      <c r="AZ17" t="n">
+      <c r="BI17" t="n">
         <v>80.76812872218812</v>
       </c>
-      <c r="BA17" t="n">
+      <c r="BJ17" t="n">
         <v>80.94249795379433</v>
       </c>
-      <c r="BB17" t="n">
+      <c r="BK17" t="n">
         <v>303</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BL17" t="n">
         <v>303</v>
       </c>
-      <c r="BD17" t="n">
+      <c r="BM17" t="n">
         <v>303</v>
       </c>
-      <c r="BE17" t="n">
+      <c r="BN17" t="n">
         <v>303</v>
       </c>
-      <c r="BF17" t="n">
+      <c r="BO17" t="n">
         <v>303</v>
       </c>
-      <c r="BG17" t="n">
+      <c r="BP17" t="n">
         <v>303</v>
       </c>
-      <c r="BH17" t="n">
+      <c r="BQ17" t="n">
         <v>303</v>
       </c>
-      <c r="BI17" t="n">
+      <c r="BR17" t="n">
         <v>303</v>
       </c>
-      <c r="BJ17" t="n">
+      <c r="BS17" t="n">
         <v>303</v>
       </c>
-      <c r="BK17" t="n">
+      <c r="BT17" t="n">
         <v>670</v>
       </c>
-      <c r="BL17" t="n">
+      <c r="BU17" t="n">
         <v>670</v>
       </c>
-      <c r="BM17" t="n">
+      <c r="BV17" t="n">
         <v>670</v>
       </c>
-      <c r="BN17" t="n">
+      <c r="BW17" t="n">
         <v>670</v>
       </c>
-      <c r="BO17" t="n">
+      <c r="BX17" t="n">
         <v>670</v>
       </c>
-      <c r="BP17" t="n">
+      <c r="BY17" t="n">
         <v>670</v>
       </c>
-      <c r="BQ17" t="n">
+      <c r="BZ17" t="n">
         <v>670</v>
       </c>
-      <c r="BR17" t="n">
+      <c r="CA17" t="n">
         <v>670</v>
       </c>
-      <c r="BS17" t="n">
+      <c r="CB17" t="n">
         <v>670</v>
       </c>
-      <c r="BT17" t="n">
+      <c r="CC17" t="n">
         <v>1</v>
       </c>
-      <c r="BU17" t="n">
+      <c r="CD17" t="n">
         <v>0.2727272727272727</v>
       </c>
-      <c r="BV17" t="n">
+      <c r="CE17" t="n">
         <v>1</v>
       </c>
-      <c r="BW17" t="n">
+      <c r="CF17" t="n">
         <v>0.9047619047619048</v>
       </c>
-      <c r="BX17" t="n">
+      <c r="CG17" t="n">
         <v>0.8846153846153846</v>
       </c>
-      <c r="BY17" t="n">
+      <c r="CH17" t="n">
         <v>0.9230769230769231</v>
       </c>
-      <c r="BZ17" t="n">
+      <c r="CI17" t="n">
         <v>0.9230769230769231</v>
       </c>
-      <c r="CA17" t="n">
+      <c r="CJ17" t="n">
         <v>0.9230769230769231</v>
       </c>
-      <c r="CB17" t="n">
+      <c r="CK17" t="n">
         <v>1</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>488.98</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4776,10 +5359,10 @@
         <v>502</v>
       </c>
       <c r="C18" t="n">
+        <v>85.9896219421794</v>
+      </c>
+      <c r="D18" t="n">
         <v>58</v>
-      </c>
-      <c r="D18" t="n">
-        <v>85.9896219421794</v>
       </c>
       <c r="E18" t="n">
         <v>502</v>
@@ -4788,228 +5371,261 @@
         <v>200</v>
       </c>
       <c r="G18" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="H18" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>510.2482200904319</v>
-      </c>
-      <c r="J18" t="n">
-        <v>73.51498737245007</v>
-      </c>
-      <c r="K18" t="n">
-        <v>525.7757779621212</v>
-      </c>
-      <c r="L18" t="n">
-        <v>77.07122946789258</v>
-      </c>
-      <c r="M18" t="n">
-        <v>517.6547704083333</v>
-      </c>
-      <c r="N18" t="n">
-        <v>80.91456773608252</v>
-      </c>
-      <c r="O18" t="n">
-        <v>517.6897254357475</v>
-      </c>
-      <c r="P18" t="n">
-        <v>78.37924594690885</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>516.9694178841565</v>
-      </c>
       <c r="R18" t="n">
-        <v>72.70301348010308</v>
+        <v>510.25</v>
       </c>
       <c r="S18" t="n">
-        <v>506.2701213280498</v>
+        <v>73.51000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>70.94927984429819</v>
+        <v>525.78</v>
       </c>
       <c r="U18" t="n">
-        <v>509.7307053273075</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>70.26943904242684</v>
+        <v>517.65</v>
       </c>
       <c r="W18" t="n">
-        <v>512.0579873552167</v>
+        <v>80.91</v>
       </c>
       <c r="X18" t="n">
-        <v>69.68802386990367</v>
+        <v>517.6900000000001</v>
       </c>
       <c r="Y18" t="n">
-        <v>512.6051045753529</v>
+        <v>78.38</v>
       </c>
       <c r="Z18" t="n">
-        <v>68.31493757099109</v>
+        <v>516.97</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>72.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>506.27</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>70.95</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>509.73</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>70.27</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>512.0599999999999</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>69.69</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>512.61</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>68.31</v>
       </c>
       <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
         <v>500.75</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AT18" t="n">
         <v>500.05</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AU18" t="n">
         <v>499.2625</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="AV18" t="n">
         <v>499.93</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="AW18" t="n">
         <v>500.1</v>
       </c>
-      <c r="AO18" t="n">
+      <c r="AX18" t="n">
         <v>499.7428571428571</v>
       </c>
-      <c r="AP18" t="n">
+      <c r="AY18" t="n">
         <v>498.35625</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AZ18" t="n">
         <v>498.5777777777778</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="BA18" t="n">
         <v>499.005</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="BB18" t="n">
         <v>97.55966123352418</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="BC18" t="n">
         <v>91.78242841996864</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="BD18" t="n">
         <v>86.6981464262645</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="BE18" t="n">
         <v>83.48248379151161</v>
       </c>
-      <c r="AW18" t="n">
+      <c r="BF18" t="n">
         <v>80.14605417611025</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="BG18" t="n">
         <v>75.44632637355716</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="BH18" t="n">
         <v>73.67821479879585</v>
       </c>
-      <c r="AZ18" t="n">
+      <c r="BI18" t="n">
         <v>73.1717883974688</v>
       </c>
-      <c r="BA18" t="n">
+      <c r="BJ18" t="n">
         <v>73.86910704076502</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BK18" t="n">
         <v>371</v>
       </c>
-      <c r="BC18" t="n">
+      <c r="BL18" t="n">
         <v>371</v>
       </c>
-      <c r="BD18" t="n">
+      <c r="BM18" t="n">
         <v>371</v>
       </c>
-      <c r="BE18" t="n">
+      <c r="BN18" t="n">
         <v>371</v>
       </c>
-      <c r="BF18" t="n">
+      <c r="BO18" t="n">
         <v>371</v>
       </c>
-      <c r="BG18" t="n">
+      <c r="BP18" t="n">
         <v>371</v>
       </c>
-      <c r="BH18" t="n">
+      <c r="BQ18" t="n">
         <v>369</v>
       </c>
-      <c r="BI18" t="n">
+      <c r="BR18" t="n">
         <v>369</v>
       </c>
-      <c r="BJ18" t="n">
+      <c r="BS18" t="n">
         <v>369</v>
       </c>
-      <c r="BK18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>669</v>
-      </c>
       <c r="BT18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC18" t="n">
         <v>1</v>
       </c>
-      <c r="BU18" t="n">
+      <c r="CD18" t="n">
         <v>1</v>
       </c>
-      <c r="BV18" t="n">
+      <c r="CE18" t="n">
         <v>0.875</v>
       </c>
-      <c r="BW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX18" t="n">
+      <c r="CF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG18" t="n">
         <v>0.8823529411764706</v>
       </c>
-      <c r="BY18" t="n">
+      <c r="CH18" t="n">
         <v>0.8823529411764706</v>
       </c>
-      <c r="BZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB18" t="n">
+      <c r="CI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK18" t="n">
         <v>1</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>512.61</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>68.31</v>
       </c>
     </row>
     <row r="19">
@@ -5022,10 +5638,10 @@
         <v>500</v>
       </c>
       <c r="C19" t="n">
+        <v>91.91994069681246</v>
+      </c>
+      <c r="D19" t="n">
         <v>62</v>
-      </c>
-      <c r="D19" t="n">
-        <v>91.91994069681246</v>
       </c>
       <c r="E19" t="n">
         <v>500</v>
@@ -5034,228 +5650,261 @@
         <v>200</v>
       </c>
       <c r="G19" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H19" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>489.2136780090993</v>
-      </c>
-      <c r="J19" t="n">
-        <v>87.11358550119823</v>
-      </c>
-      <c r="K19" t="n">
-        <v>479.5436686391766</v>
-      </c>
-      <c r="L19" t="n">
-        <v>71.14748664867757</v>
-      </c>
-      <c r="M19" t="n">
-        <v>503.9859014971228</v>
-      </c>
-      <c r="N19" t="n">
-        <v>80.63412758136928</v>
-      </c>
-      <c r="O19" t="n">
-        <v>503.6712678798199</v>
-      </c>
-      <c r="P19" t="n">
-        <v>84.9934989071876</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>501.922800222327</v>
-      </c>
       <c r="R19" t="n">
-        <v>78.07515160830573</v>
+        <v>489.21</v>
       </c>
       <c r="S19" t="n">
-        <v>503.8824337498385</v>
+        <v>87.11</v>
       </c>
       <c r="T19" t="n">
-        <v>77.93811032504836</v>
+        <v>479.54</v>
       </c>
       <c r="U19" t="n">
-        <v>502.8486070034426</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>78.57715113263376</v>
+        <v>503.99</v>
       </c>
       <c r="W19" t="n">
-        <v>508.3995119115674</v>
+        <v>80.63</v>
       </c>
       <c r="X19" t="n">
-        <v>76.13698810380022</v>
+        <v>503.67</v>
       </c>
       <c r="Y19" t="n">
-        <v>503.6967412884291</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="Z19" t="n">
-        <v>74.29855154938396</v>
+        <v>501.92</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>78.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>503.88</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>77.94</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>502.85</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>78.58</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>508.4</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>76.14</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>503.7</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>74.3</v>
       </c>
       <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
         <v>501.2</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AT19" t="n">
         <v>500.3833333333333</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AU19" t="n">
         <v>499.6875</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AV19" t="n">
         <v>499.85</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AW19" t="n">
         <v>501.8083333333333</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="AX19" t="n">
         <v>503.5928571428572</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AY19" t="n">
         <v>506.9875</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AZ19" t="n">
         <v>506.1</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="BA19" t="n">
         <v>505.175</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="BB19" t="n">
         <v>109.3787456501491</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="BC19" t="n">
         <v>96.86022432121224</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="BD19" t="n">
         <v>88.40907670454432</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="BE19" t="n">
         <v>96.93486214979625</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="BF19" t="n">
         <v>93.88390843956641</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="BG19" t="n">
         <v>92.98063519038878</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="BH19" t="n">
         <v>92.91723383608662</v>
       </c>
-      <c r="AZ19" t="n">
+      <c r="BI19" t="n">
         <v>91.89499442298259</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BJ19" t="n">
         <v>90.90348934446905</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BK19" t="n">
         <v>339</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BL19" t="n">
         <v>339</v>
       </c>
-      <c r="BD19" t="n">
+      <c r="BM19" t="n">
         <v>339</v>
       </c>
-      <c r="BE19" t="n">
+      <c r="BN19" t="n">
         <v>339</v>
       </c>
-      <c r="BF19" t="n">
+      <c r="BO19" t="n">
         <v>339</v>
       </c>
-      <c r="BG19" t="n">
+      <c r="BP19" t="n">
         <v>339</v>
       </c>
-      <c r="BH19" t="n">
+      <c r="BQ19" t="n">
         <v>339</v>
       </c>
-      <c r="BI19" t="n">
+      <c r="BR19" t="n">
         <v>339</v>
       </c>
-      <c r="BJ19" t="n">
+      <c r="BS19" t="n">
         <v>339</v>
       </c>
-      <c r="BK19" t="n">
+      <c r="BT19" t="n">
         <v>654</v>
       </c>
-      <c r="BL19" t="n">
+      <c r="BU19" t="n">
         <v>654</v>
       </c>
-      <c r="BM19" t="n">
+      <c r="BV19" t="n">
         <v>654</v>
       </c>
-      <c r="BN19" t="n">
+      <c r="BW19" t="n">
         <v>654</v>
       </c>
-      <c r="BO19" t="n">
+      <c r="BX19" t="n">
         <v>654</v>
       </c>
-      <c r="BP19" t="n">
+      <c r="BY19" t="n">
         <v>654</v>
       </c>
-      <c r="BQ19" t="n">
+      <c r="BZ19" t="n">
         <v>654</v>
       </c>
-      <c r="BR19" t="n">
+      <c r="CA19" t="n">
         <v>654</v>
       </c>
-      <c r="BS19" t="n">
+      <c r="CB19" t="n">
         <v>654</v>
       </c>
-      <c r="BT19" t="n">
+      <c r="CC19" t="n">
         <v>0.8</v>
       </c>
-      <c r="BU19" t="n">
+      <c r="CD19" t="n">
         <v>0.8</v>
       </c>
-      <c r="BV19" t="n">
+      <c r="CE19" t="n">
         <v>0.8</v>
       </c>
-      <c r="BW19" t="n">
+      <c r="CF19" t="n">
         <v>0.9</v>
       </c>
-      <c r="BX19" t="n">
+      <c r="CG19" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="BY19" t="n">
+      <c r="CH19" t="n">
         <v>0.7857142857142857</v>
       </c>
-      <c r="BZ19" t="n">
+      <c r="CI19" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="CA19" t="n">
+      <c r="CJ19" t="n">
         <v>0.7826086956521739</v>
       </c>
-      <c r="CB19" t="n">
+      <c r="CK19" t="n">
         <v>0.9130434782608695</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>503.7</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>74.3</v>
       </c>
     </row>
     <row r="20">
@@ -5268,10 +5917,10 @@
         <v>499</v>
       </c>
       <c r="C20" t="n">
+        <v>91.91994069681246</v>
+      </c>
+      <c r="D20" t="n">
         <v>62</v>
-      </c>
-      <c r="D20" t="n">
-        <v>91.91994069681246</v>
       </c>
       <c r="E20" t="n">
         <v>499</v>
@@ -5280,228 +5929,261 @@
         <v>200</v>
       </c>
       <c r="G20" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="H20" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>522.8686999069835</v>
-      </c>
-      <c r="J20" t="n">
-        <v>65.28345548557132</v>
-      </c>
-      <c r="K20" t="n">
-        <v>503.9766331408386</v>
-      </c>
-      <c r="L20" t="n">
-        <v>69.78230260897776</v>
-      </c>
-      <c r="M20" t="n">
-        <v>502.8523356838646</v>
-      </c>
-      <c r="N20" t="n">
-        <v>79.20262639994772</v>
-      </c>
-      <c r="O20" t="n">
-        <v>501.1957045707041</v>
-      </c>
-      <c r="P20" t="n">
-        <v>71.32589374033122</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>499.9466857824396</v>
-      </c>
       <c r="R20" t="n">
-        <v>70.87057627088636</v>
+        <v>522.87</v>
       </c>
       <c r="S20" t="n">
-        <v>493.2712509310696</v>
+        <v>65.28</v>
       </c>
       <c r="T20" t="n">
-        <v>68.49993964364612</v>
+        <v>503.98</v>
       </c>
       <c r="U20" t="n">
-        <v>490.6862697429815</v>
+        <v>69.78</v>
       </c>
       <c r="V20" t="n">
-        <v>68.93934376239444</v>
+        <v>502.85</v>
       </c>
       <c r="W20" t="n">
-        <v>492.4645864215459</v>
+        <v>79.2</v>
       </c>
       <c r="X20" t="n">
-        <v>70.09643480502372</v>
+        <v>501.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>489.3085103872564</v>
+        <v>71.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>69.46759281390527</v>
+        <v>499.95</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>70.87</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>493.27</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>68.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>490.69</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>68.94</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>492.46</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>489.31</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>69.47</v>
       </c>
       <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
         <v>498.45</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AT20" t="n">
         <v>498.5666666666667</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AU20" t="n">
         <v>498.4375</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AV20" t="n">
         <v>497.7</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AW20" t="n">
         <v>497.1</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AX20" t="n">
         <v>497.5714285714286</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AY20" t="n">
         <v>498.36875</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AZ20" t="n">
         <v>499.4833333333333</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="BA20" t="n">
         <v>500.39</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="BB20" t="n">
         <v>79.34984246991296</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="BC20" t="n">
         <v>77.63662509122582</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="BD20" t="n">
         <v>80.23338515699061</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="BE20" t="n">
         <v>81.03770727260242</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="BF20" t="n">
         <v>77.86541808359686</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="BG20" t="n">
         <v>75.39544727228399</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="BH20" t="n">
         <v>75.33787409688104</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="BI20" t="n">
         <v>76.81141950691099</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BJ20" t="n">
         <v>76.41621490233601</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BK20" t="n">
         <v>360</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BL20" t="n">
         <v>360</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BM20" t="n">
         <v>360</v>
       </c>
-      <c r="BE20" t="n">
+      <c r="BN20" t="n">
         <v>360</v>
       </c>
-      <c r="BF20" t="n">
+      <c r="BO20" t="n">
         <v>360</v>
       </c>
-      <c r="BG20" t="n">
+      <c r="BP20" t="n">
         <v>360</v>
       </c>
-      <c r="BH20" t="n">
+      <c r="BQ20" t="n">
         <v>360</v>
       </c>
-      <c r="BI20" t="n">
+      <c r="BR20" t="n">
         <v>360</v>
       </c>
-      <c r="BJ20" t="n">
+      <c r="BS20" t="n">
         <v>360</v>
       </c>
-      <c r="BK20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>669</v>
-      </c>
       <c r="BT20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC20" t="n">
         <v>0.6153846153846154</v>
       </c>
-      <c r="BU20" t="n">
+      <c r="CD20" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="BV20" t="n">
+      <c r="CE20" t="n">
         <v>0.6086956521739131</v>
       </c>
-      <c r="BW20" t="n">
+      <c r="CF20" t="n">
         <v>0.6521739130434783</v>
       </c>
-      <c r="BX20" t="n">
+      <c r="CG20" t="n">
         <v>0.6521739130434783</v>
       </c>
-      <c r="BY20" t="n">
+      <c r="CH20" t="n">
         <v>0.8260869565217391</v>
       </c>
-      <c r="BZ20" t="n">
+      <c r="CI20" t="n">
         <v>0.9130434782608695</v>
       </c>
-      <c r="CA20" t="n">
+      <c r="CJ20" t="n">
         <v>0.9583333333333334</v>
       </c>
-      <c r="CB20" t="n">
+      <c r="CK20" t="n">
         <v>0.8</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>489.31</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>69.47</v>
       </c>
     </row>
     <row r="21">
@@ -5514,10 +6196,10 @@
         <v>499</v>
       </c>
       <c r="C21" t="n">
+        <v>85.9896219421794</v>
+      </c>
+      <c r="D21" t="n">
         <v>58</v>
-      </c>
-      <c r="D21" t="n">
-        <v>85.9896219421794</v>
       </c>
       <c r="E21" t="n">
         <v>499</v>
@@ -5526,228 +6208,261 @@
         <v>200</v>
       </c>
       <c r="G21" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="H21" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>500.8337977429976</v>
-      </c>
-      <c r="J21" t="n">
-        <v>86.14278034889468</v>
-      </c>
-      <c r="K21" t="n">
-        <v>486.0696373674244</v>
-      </c>
-      <c r="L21" t="n">
-        <v>79.32773394609849</v>
-      </c>
-      <c r="M21" t="n">
-        <v>494.6223132979798</v>
-      </c>
-      <c r="N21" t="n">
-        <v>78.21560299196935</v>
-      </c>
-      <c r="O21" t="n">
-        <v>491.7581667064065</v>
-      </c>
-      <c r="P21" t="n">
-        <v>83.87909943917315</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>492.9806047696883</v>
-      </c>
       <c r="R21" t="n">
-        <v>78.41608217149336</v>
+        <v>500.83</v>
       </c>
       <c r="S21" t="n">
-        <v>496.2844116672003</v>
+        <v>86.14</v>
       </c>
       <c r="T21" t="n">
-        <v>75.53762401998691</v>
+        <v>486.07</v>
       </c>
       <c r="U21" t="n">
-        <v>495.7831543096053</v>
+        <v>79.33</v>
       </c>
       <c r="V21" t="n">
-        <v>72.21909735607971</v>
+        <v>494.62</v>
       </c>
       <c r="W21" t="n">
-        <v>497.4407564082133</v>
+        <v>78.22</v>
       </c>
       <c r="X21" t="n">
-        <v>74.51983372648101</v>
+        <v>491.76</v>
       </c>
       <c r="Y21" t="n">
-        <v>491.9553062789064</v>
+        <v>83.88</v>
       </c>
       <c r="Z21" t="n">
-        <v>75.39681909005243</v>
+        <v>492.98</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>78.42</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>496.28</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>495.78</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>72.22</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>497.44</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>74.52</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>491.96</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
         <v>501.25</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AT21" t="n">
         <v>499.85</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AU21" t="n">
         <v>499.6</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AV21" t="n">
         <v>499.85</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AW21" t="n">
         <v>499.3083333333333</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AX21" t="n">
         <v>498.9928571428571</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AY21" t="n">
         <v>500.175</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AZ21" t="n">
         <v>499.5166666666667</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="BA21" t="n">
         <v>500.72</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="BB21" t="n">
         <v>104.0095548495425</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="BC21" t="n">
         <v>96.15071935941683</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="BD21" t="n">
         <v>91.72071739797939</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="BE21" t="n">
         <v>93.1064310345961</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="BF21" t="n">
         <v>88.73544912015466</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="BG21" t="n">
         <v>84.54816855569639</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="BH21" t="n">
         <v>82.89681462517122</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="BI21" t="n">
         <v>85.27351256072689</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BJ21" t="n">
         <v>85.26125497551628</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BK21" t="n">
         <v>312</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BL21" t="n">
         <v>312</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BM21" t="n">
         <v>312</v>
       </c>
-      <c r="BE21" t="n">
+      <c r="BN21" t="n">
         <v>312</v>
       </c>
-      <c r="BF21" t="n">
+      <c r="BO21" t="n">
         <v>312</v>
       </c>
-      <c r="BG21" t="n">
+      <c r="BP21" t="n">
         <v>312</v>
       </c>
-      <c r="BH21" t="n">
+      <c r="BQ21" t="n">
         <v>312</v>
       </c>
-      <c r="BI21" t="n">
+      <c r="BR21" t="n">
         <v>312</v>
       </c>
-      <c r="BJ21" t="n">
+      <c r="BS21" t="n">
         <v>312</v>
       </c>
-      <c r="BK21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>669</v>
-      </c>
       <c r="BT21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC21" t="n">
         <v>1</v>
       </c>
-      <c r="BU21" t="n">
+      <c r="CD21" t="n">
         <v>0.8</v>
       </c>
-      <c r="BV21" t="n">
+      <c r="CE21" t="n">
         <v>0.7857142857142857</v>
       </c>
-      <c r="BW21" t="n">
+      <c r="CF21" t="n">
         <v>0.8125</v>
       </c>
-      <c r="BX21" t="n">
+      <c r="CG21" t="n">
         <v>0.875</v>
       </c>
-      <c r="BY21" t="n">
+      <c r="CH21" t="n">
         <v>0.875</v>
       </c>
-      <c r="BZ21" t="n">
+      <c r="CI21" t="n">
         <v>1</v>
       </c>
-      <c r="CA21" t="n">
+      <c r="CJ21" t="n">
         <v>1</v>
       </c>
-      <c r="CB21" t="n">
+      <c r="CK21" t="n">
         <v>1</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>491.96</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>75.40000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -5760,10 +6475,10 @@
         <v>499.65</v>
       </c>
       <c r="C22" t="n">
+        <v>87.76871756856931</v>
+      </c>
+      <c r="D22" t="n">
         <v>59.2</v>
-      </c>
-      <c r="D22" t="n">
-        <v>87.76871756856931</v>
       </c>
       <c r="E22" t="n">
         <v>499.65</v>
@@ -5772,224 +6487,239 @@
         <v>200</v>
       </c>
       <c r="G22" t="n">
-        <v>0.51275</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>77.325</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.696</v>
+      </c>
       <c r="I22" t="n">
-        <v>500.1730027305381</v>
+        <v>2.774</v>
       </c>
       <c r="J22" t="n">
-        <v>64.93365152456022</v>
+        <v>2.84</v>
       </c>
       <c r="K22" t="n">
-        <v>497.7017264870807</v>
+        <v>2.8895</v>
       </c>
       <c r="L22" t="n">
-        <v>71.79507248765408</v>
+        <v>2.9185</v>
       </c>
       <c r="M22" t="n">
-        <v>498.1275882139633</v>
+        <v>2.932</v>
       </c>
       <c r="N22" t="n">
-        <v>73.15265086376834</v>
+        <v>2.43</v>
       </c>
       <c r="O22" t="n">
-        <v>497.295478489892</v>
+        <v>2.5155</v>
       </c>
       <c r="P22" t="n">
-        <v>72.06616052110293</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>498.3018140924448</v>
-      </c>
+        <v>2.5935</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>70.9125889634054</v>
+        <v>500.1729999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>496.4387969852939</v>
+        <v>64.93350000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>69.82261459972935</v>
+        <v>497.7015</v>
       </c>
       <c r="U22" t="n">
-        <v>495.9694552081058</v>
+        <v>71.79549999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>69.7230571615484</v>
+        <v>498.128</v>
       </c>
       <c r="W22" t="n">
-        <v>497.6489694872232</v>
+        <v>73.1525</v>
       </c>
       <c r="X22" t="n">
-        <v>69.3271650243847</v>
+        <v>497.2955000000001</v>
       </c>
       <c r="Y22" t="n">
-        <v>495.790163775651</v>
+        <v>72.06699999999998</v>
       </c>
       <c r="Z22" t="n">
-        <v>69.09495904382638</v>
+        <v>498.302</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>70.91249999999999</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>496.4385</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>69.82250000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>495.9685000000001</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>69.72299999999998</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>497.649</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>69.32750000000001</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>495.7895</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>69.0945</v>
       </c>
       <c r="AJ22" t="n">
-        <v>499.835</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>499.5691666666667</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>499.46875</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>499.8355</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>499.5685</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>499.4690000000001</v>
+      </c>
+      <c r="AV22" t="n">
         <v>499.4420000000001</v>
       </c>
-      <c r="AN22" t="n">
-        <v>499.56375</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>499.492142857143</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>499.8809375</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>499.8091666666667</v>
-      </c>
-      <c r="AR22" t="n">
+      <c r="AW22" t="n">
+        <v>499.5634999999999</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>499.4915</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>499.8815000000001</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>499.809</v>
+      </c>
+      <c r="BA22" t="n">
         <v>499.7969999999999</v>
       </c>
-      <c r="AS22" t="n">
-        <v>95.02772201977663</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>88.06579651706346</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>85.62348341742282</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>84.20340555789717</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>82.12505500617623</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>80.26262574121583</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>79.34411532129474</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>78.93894381255139</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>78.69967726035233</v>
-      </c>
       <c r="BB22" t="n">
+        <v>95.02699999999999</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>88.06699999999999</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>85.62300000000002</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>84.20349999999999</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>82.1255</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>80.26349999999999</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>79.34400000000001</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>78.938</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>78.6995</v>
+      </c>
+      <c r="BK22" t="n">
         <v>340.35</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BL22" t="n">
         <v>340.35</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BM22" t="n">
         <v>340.35</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BN22" t="n">
         <v>340.35</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BO22" t="n">
         <v>340.2</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BP22" t="n">
         <v>339.65</v>
       </c>
-      <c r="BH22" t="n">
+      <c r="BQ22" t="n">
         <v>339.4</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BR22" t="n">
         <v>338.6</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BS22" t="n">
         <v>338.1</v>
       </c>
-      <c r="BK22" t="n">
+      <c r="BT22" t="n">
         <v>663.3</v>
       </c>
-      <c r="BL22" t="n">
+      <c r="BU22" t="n">
         <v>663.3</v>
       </c>
-      <c r="BM22" t="n">
+      <c r="BV22" t="n">
         <v>663.3</v>
       </c>
-      <c r="BN22" t="n">
+      <c r="BW22" t="n">
         <v>663.3</v>
       </c>
-      <c r="BO22" t="n">
+      <c r="BX22" t="n">
         <v>663.3</v>
       </c>
-      <c r="BP22" t="n">
+      <c r="BY22" t="n">
         <v>663.3</v>
       </c>
-      <c r="BQ22" t="n">
+      <c r="BZ22" t="n">
         <v>663.4</v>
       </c>
-      <c r="BR22" t="n">
+      <c r="CA22" t="n">
         <v>663.4</v>
       </c>
-      <c r="BS22" t="n">
+      <c r="CB22" t="n">
         <v>663.4</v>
       </c>
-      <c r="BT22" t="n">
-        <v>0.7535016372516373</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>0.7025325392701555</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>0.7691913500436687</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>0.7874573763178387</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>0.8608839090725111</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>0.8208779022100128</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>0.8272222438638434</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>0.8519441561489616</v>
-      </c>
-      <c r="CB22" t="n">
-        <v>0.888692984999226</v>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="n">
+        <v>495.7895</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>69.0945</v>
       </c>
     </row>
     <row r="23">
@@ -6002,10 +6732,10 @@
         <v>1.136708081768532</v>
       </c>
       <c r="C23" t="n">
+        <v>2.336749964870013</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.576137851304825</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.336749964870013</v>
       </c>
       <c r="E23" t="n">
         <v>1.136708081768532</v>
@@ -6014,224 +6744,239 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.02953476987516489</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>0.8315331433088237</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2465424058752101</v>
+      </c>
       <c r="I23" t="n">
-        <v>30.09895371968305</v>
+        <v>0.2495764833725958</v>
       </c>
       <c r="J23" t="n">
-        <v>19.04859276441433</v>
+        <v>0.2216683155195238</v>
       </c>
       <c r="K23" t="n">
-        <v>22.30705691650806</v>
+        <v>0.1857977111637391</v>
       </c>
       <c r="L23" t="n">
-        <v>9.857564403467389</v>
+        <v>0.1692794326425673</v>
       </c>
       <c r="M23" t="n">
-        <v>16.35887626169773</v>
+        <v>0.1591953450787329</v>
       </c>
       <c r="N23" t="n">
-        <v>9.152516529804359</v>
+        <v>0.3527336851387728</v>
       </c>
       <c r="O23" t="n">
-        <v>12.91980553593794</v>
+        <v>0.2382275559649903</v>
       </c>
       <c r="P23" t="n">
-        <v>9.532049500889668</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>9.594638446432278</v>
-      </c>
+        <v>0.2333796319981222</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>7.64541588061133</v>
+        <v>30.09979630985459</v>
       </c>
       <c r="S23" t="n">
-        <v>8.777153515551557</v>
+        <v>19.04882764040045</v>
       </c>
       <c r="T23" t="n">
-        <v>6.659676160217264</v>
+        <v>22.30772070146873</v>
       </c>
       <c r="U23" t="n">
-        <v>8.371415175180633</v>
+        <v>9.85679593238247</v>
       </c>
       <c r="V23" t="n">
-        <v>6.155987265282022</v>
+        <v>16.35889219000511</v>
       </c>
       <c r="W23" t="n">
-        <v>9.247352391959375</v>
+        <v>9.152354816341559</v>
       </c>
       <c r="X23" t="n">
-        <v>6.820162502985132</v>
+        <v>12.92032037854367</v>
       </c>
       <c r="Y23" t="n">
-        <v>8.543413431696401</v>
+        <v>9.531562582449842</v>
       </c>
       <c r="Z23" t="n">
-        <v>6.743861797072762</v>
+        <v>9.595331430605089</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>7.647089487614157</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>8.77643751908003</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>6.660227493348699</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>8.372525416032204</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>6.156678102934886</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>9.247236799231031</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>6.820741490020291</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>8.543017755361451</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>6.744643469177285</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.242199930049898</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.440884586569265</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.299091914620205</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.241419839016515</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1.441024032817598</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.298962744087115</v>
+      </c>
+      <c r="AV23" t="n">
         <v>1.209439191482874</v>
       </c>
-      <c r="AN23" t="n">
-        <v>1.527260272533291</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1.922936490782585</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>2.043619196482132</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.873327085620826</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.830786716141454</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>13.93561266124575</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>10.56027106984492</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>8.694211812665595</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>9.144715036985964</v>
-      </c>
       <c r="AW23" t="n">
-        <v>7.86729038445305</v>
+        <v>1.528312709114888</v>
       </c>
       <c r="AX23" t="n">
-        <v>7.610502519291364</v>
+        <v>1.922860465145884</v>
       </c>
       <c r="AY23" t="n">
-        <v>7.285977162580016</v>
+        <v>2.044361372422362</v>
       </c>
       <c r="AZ23" t="n">
-        <v>7.603116564117207</v>
+        <v>1.873296840501149</v>
       </c>
       <c r="BA23" t="n">
-        <v>7.592926009494808</v>
+        <v>1.832355688293366</v>
       </c>
       <c r="BB23" t="n">
+        <v>13.9357050319258</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>10.559011167818</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>8.693373217269395</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>9.143646787739964</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>7.867327155962649</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>7.611001230905308</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>7.288104511354174</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>7.602550541551308</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>7.592553467569047</v>
+      </c>
+      <c r="BK23" t="n">
         <v>29.52657144086715</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BL23" t="n">
         <v>29.52657144086715</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BM23" t="n">
         <v>29.52657144086715</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BN23" t="n">
         <v>29.52657144086715</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BO23" t="n">
         <v>29.31067705587308</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BP23" t="n">
         <v>28.47394931290151</v>
       </c>
-      <c r="BH23" t="n">
+      <c r="BQ23" t="n">
         <v>28.15446117776944</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BR23" t="n">
         <v>26.95493314873238</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BS23" t="n">
         <v>26.46924730005708</v>
       </c>
-      <c r="BK23" t="n">
+      <c r="BT23" t="n">
         <v>22.07904460175566</v>
       </c>
-      <c r="BL23" t="n">
+      <c r="BU23" t="n">
         <v>22.07904460175566</v>
       </c>
-      <c r="BM23" t="n">
+      <c r="BV23" t="n">
         <v>22.07904460175566</v>
       </c>
-      <c r="BN23" t="n">
+      <c r="BW23" t="n">
         <v>22.07904460175566</v>
       </c>
-      <c r="BO23" t="n">
+      <c r="BX23" t="n">
         <v>22.07904460175566</v>
       </c>
-      <c r="BP23" t="n">
+      <c r="BY23" t="n">
         <v>22.07904460175566</v>
       </c>
-      <c r="BQ23" t="n">
+      <c r="BZ23" t="n">
         <v>21.97223127878507</v>
       </c>
-      <c r="BR23" t="n">
+      <c r="CA23" t="n">
         <v>21.97223127878507</v>
       </c>
-      <c r="BS23" t="n">
+      <c r="CB23" t="n">
         <v>21.97223127878507</v>
       </c>
-      <c r="BT23" t="n">
-        <v>0.2276490542360139</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>0.2454630140641622</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>0.1858741385335856</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>0.2114616167154891</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>0.09310682058338518</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>0.1981333771816847</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>0.2206129946256798</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>0.2277798483421797</v>
-      </c>
-      <c r="CB23" t="n">
-        <v>0.1059972022379631</v>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr"/>
+      <c r="CH23" t="inlineStr"/>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="inlineStr"/>
+      <c r="CK23" t="inlineStr"/>
+      <c r="CL23" t="n">
+        <v>8.543017755361451</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>6.744643469177285</v>
       </c>
     </row>
   </sheetData>
